--- a/Supplemental Files/Table S2.xlsx
+++ b/Supplemental Files/Table S2.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Šimon Pavlů\Desktop\2. Differencial analysis of barley promoterome\Supplement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56EACAF1-3F09-4630-A66A-878C339FA6BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B050D19E-0EA3-467A-8521-71CFDE3043B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="List1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="162913" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -720,22 +720,22 @@
         <v>9</v>
       </c>
       <c r="B3" s="5">
-        <v>679</v>
+        <v>618</v>
       </c>
       <c r="C3" s="5">
-        <v>802</v>
+        <v>719</v>
       </c>
       <c r="D3" s="5">
-        <v>680</v>
+        <v>602</v>
       </c>
       <c r="E3" s="2">
-        <v>714</v>
+        <v>631</v>
       </c>
       <c r="F3" s="2">
-        <v>667</v>
+        <v>597</v>
       </c>
       <c r="G3" s="2">
-        <v>806</v>
+        <v>721</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">

--- a/Supplemental Files/Table S2.xlsx
+++ b/Supplemental Files/Table S2.xlsx
@@ -1,67 +1,90 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Šimon Pavlů\Desktop\2. Differencial analysis of barley promoterome\Supplement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B050D19E-0EA3-467A-8521-71CFDE3043B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F186714-BA58-48C4-8D44-2886A47CB28C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="List1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913" iterateDelta="1E-4"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
-    <t>Dataset</t>
+    <t>TATAxTATA</t>
   </si>
   <si>
-    <t>4DAGx24DAP</t>
+    <r>
+      <t xml:space="preserve">TableS3B - Number of </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>unique</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> long shifts per gene (unique shifts differ in at least one of the shifting TSS locations, hence the TATA-box presence might change)</t>
+    </r>
   </si>
   <si>
-    <t>4DAGx8DAP</t>
+    <t>Count</t>
   </si>
   <si>
-    <t>24DAPx8DAP</t>
+    <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t>8DAPxINF</t>
+    <t>TATAxTATAless</t>
   </si>
   <si>
-    <t>24DAPxINF</t>
-  </si>
-  <si>
-    <t>4DAGxINF</t>
-  </si>
-  <si>
-    <t>TableS2 - Number of long and short shifts identified between samples</t>
-  </si>
-  <si>
-    <t>short</t>
-  </si>
-  <si>
-    <t>long</t>
+    <t>TATAlessxTATAless</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -75,6 +98,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -84,7 +116,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -153,102 +185,22 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normální" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="11">
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
+  <dxfs count="8">
     <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
@@ -397,16 +349,13 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{FF5395E5-B4A4-4778-97E4-C989B5A4B1EA}" name="Tabulka1" displayName="Tabulka1" ref="A2:G4" totalsRowShown="0" headerRowDxfId="10" headerRowBorderDxfId="9" tableBorderDxfId="8" totalsRowBorderDxfId="7">
-  <autoFilter ref="A2:G4" xr:uid="{FF5395E5-B4A4-4778-97E4-C989B5A4B1EA}"/>
-  <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{55A74C76-9995-40D1-897A-03119A8BB5C3}" name="Dataset" dataDxfId="6"/>
-    <tableColumn id="5" xr3:uid="{74E46096-9FB1-4FDA-A932-8755E97A6785}" name="4DAGx24DAP" dataDxfId="5"/>
-    <tableColumn id="6" xr3:uid="{308B2A84-B0D5-45CE-88A5-0E54865761C9}" name="4DAGx8DAP" dataDxfId="4"/>
-    <tableColumn id="7" xr3:uid="{A8BBC836-EE97-44D0-AAB7-D99007FC5765}" name="24DAPx8DAP" dataDxfId="3"/>
-    <tableColumn id="2" xr3:uid="{D16DF18A-B9F9-4D5B-8C2A-99067EFA81B5}" name="8DAPxINF" dataDxfId="2"/>
-    <tableColumn id="3" xr3:uid="{56E1EAEE-BFC5-4CD6-8BAA-C676A6B074BB}" name="24DAPxINF" dataDxfId="1"/>
-    <tableColumn id="4" xr3:uid="{BCF8AFE1-87DC-4877-96DE-9384D3631B7B}" name="4DAGxINF" dataDxfId="0"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{CA5135F6-47C6-4F1D-AB67-C984EEF8E261}" name="Tabulka14" displayName="Tabulka14" ref="A2:D3" totalsRowShown="0" headerRowDxfId="7" headerRowBorderDxfId="6" tableBorderDxfId="5" totalsRowBorderDxfId="4">
+  <autoFilter ref="A2:D3" xr:uid="{CA5135F6-47C6-4F1D-AB67-C984EEF8E261}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{0EF8FA16-B462-4E63-94A2-8CBDA63A3F8B}" name=" " dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{253C3C3B-4139-49ED-8C55-DC4B5224BF54}" name="TATAxTATA" dataDxfId="2"/>
+    <tableColumn id="6" xr3:uid="{3D4BA074-F54C-4E70-B409-E3D34634B585}" name="TATAxTATAless" dataDxfId="1"/>
+    <tableColumn id="7" xr3:uid="{E50E6742-CDD4-4640-8D93-78B4903FCF77}" name="TATAlessxTATAless" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -675,92 +624,53 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.44140625" customWidth="1"/>
     <col min="2" max="2" width="14.44140625" customWidth="1"/>
-    <col min="3" max="3" width="13.5546875" customWidth="1"/>
-    <col min="4" max="4" width="14.6640625" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="19.33203125" customWidth="1"/>
     <col min="5" max="5" width="14.44140625" customWidth="1"/>
     <col min="6" max="6" width="13.33203125" customWidth="1"/>
     <col min="7" max="7" width="14.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>1</v>
-      </c>
       <c r="C2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>6</v>
+      <c r="B3" s="4">
+        <v>19</v>
+      </c>
+      <c r="C3" s="4">
+        <v>305</v>
+      </c>
+      <c r="D3" s="4">
+        <v>1805</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="5">
-        <v>618</v>
-      </c>
-      <c r="C3" s="5">
-        <v>719</v>
-      </c>
-      <c r="D3" s="5">
-        <v>602</v>
-      </c>
-      <c r="E3" s="2">
-        <v>631</v>
-      </c>
-      <c r="F3" s="2">
-        <v>597</v>
-      </c>
-      <c r="G3" s="2">
-        <v>721</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="5">
-        <v>4939</v>
-      </c>
-      <c r="C4" s="5">
-        <v>6816</v>
-      </c>
-      <c r="D4" s="5">
-        <v>6347</v>
-      </c>
-      <c r="E4" s="6">
-        <v>5706</v>
-      </c>
-      <c r="F4" s="6">
-        <v>5156</v>
-      </c>
-      <c r="G4" s="6">
-        <v>5393</v>
-      </c>
-    </row>
+    <row r="4" spans="1:4" ht="16.2" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="5" spans="1:4" ht="13.8" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Supplemental Files/Table S2.xlsx
+++ b/Supplemental Files/Table S2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Šimon Pavlů\Desktop\2. Differencial analysis of barley promoterome\Supplement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F186714-BA58-48C4-8D44-2886A47CB28C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BC9478C-4844-4AE6-BD49-7FF1A1495DFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,8 +41,39 @@
     <t>TATAxTATA</t>
   </si>
   <si>
+    <t>Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>TATAxTATAless</t>
+  </si>
+  <si>
+    <t>TATAlessxTATAless</t>
+  </si>
+  <si>
     <r>
-      <t xml:space="preserve">TableS3B - Number of </t>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>TableS2.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> - Number of </t>
     </r>
     <r>
       <rPr>
@@ -67,29 +98,25 @@
       <t xml:space="preserve"> long shifts per gene (unique shifts differ in at least one of the shifting TSS locations, hence the TATA-box presence might change)</t>
     </r>
   </si>
-  <si>
-    <t>Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
-    <t>TATAxTATAless</t>
-  </si>
-  <si>
-    <t>TATAlessxTATAless</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -189,13 +216,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normální" xfId="0" builtinId="0"/>
@@ -637,27 +665,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>1</v>
+      <c r="A1" s="6" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>4</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3" s="4">
         <v>19</v>
@@ -672,7 +700,7 @@
     <row r="4" spans="1:4" ht="16.2" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="5" spans="1:4" ht="13.8" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>

--- a/Supplemental Files/Table S2.xlsx
+++ b/Supplemental Files/Table S2.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Šimon Pavlů\Desktop\2. Differencial analysis of barley promoterome\Supplement\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Šimon Pavlů\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E574E28-CA8F-4763-820B-A1954658C5A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49461A0E-7A67-4613-96EA-960F3C98F919}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1903,18 +1903,6 @@
     <t>HORVU.MOREX.r3.3HG0303530</t>
   </si>
   <si>
-    <t>n = indicates the number of terms in which a gene appears.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mean_log2FC = is the mean log2 fold-change across pairwise contrasts, preserving direction of change. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">max_abs_log2FC = is the largest absolute log2 fold-change observed across contrasts. </t>
-  </si>
-  <si>
-    <t>score = combines term frequency and effect size (log1p(n) × max_abs_log2FC).</t>
-  </si>
-  <si>
     <t>Apyrase</t>
   </si>
   <si>
@@ -3341,28 +3329,59 @@
       <rPr>
         <b/>
         <sz val="11"/>
-        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="238"/>
       </rPr>
-      <t>Table S3</t>
+      <t>Table S2</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
-        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
       </rPr>
-      <t xml:space="preserve">. List of putative core genes underlying GO term enrichment ranked by a combined score integrating GO term contribution and expression change. </t>
+      <t xml:space="preserve">. </t>
     </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>List of genes with the top contribution to the GO term enrichment.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t xml:space="preserve"> The genes are ranked by a score combining the number of GO terms, in which a gene appears, and the magnitude of its expression change.</t>
+    </r>
+  </si>
+  <si>
+    <t>n - the number of terms in which a gene appears</t>
+  </si>
+  <si>
+    <t>mean_log2FC - the mean log2 fold-change across pairwise contrasts</t>
+  </si>
+  <si>
+    <t>max_abs_log2FC - the largest absolute log2 fold-change observed across contrasts</t>
+  </si>
+  <si>
+    <t>score - a parameter combining a GO term frequency and effect size (log1p(n) × max_abs_log2FC)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -3372,23 +3391,29 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="238"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="238"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -3411,11 +3436,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normální" xfId="0" builtinId="0"/>
@@ -3717,39 +3747,39 @@
   <cols>
     <col min="1" max="1" width="99.5546875" customWidth="1"/>
     <col min="3" max="3" width="12.33203125" customWidth="1"/>
-    <col min="4" max="4" width="15.21875" customWidth="1"/>
+    <col min="4" max="4" width="15.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
+        <v>1101</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="4" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
         <v>1105</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>627</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>628</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>629</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>630</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>0</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C8" t="s">
@@ -3762,7 +3792,7 @@
         <v>4</v>
       </c>
       <c r="F8" t="s">
-        <v>1104</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -3782,7 +3812,7 @@
         <v>36.720586151965598</v>
       </c>
       <c r="F9" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -3802,7 +3832,7 @@
         <v>36.379908711123903</v>
       </c>
       <c r="F10" t="s">
-        <v>632</v>
+        <v>628</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -3822,7 +3852,7 @@
         <v>29.5983983257643</v>
       </c>
       <c r="F11" t="s">
-        <v>633</v>
+        <v>629</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
@@ -3842,7 +3872,7 @@
         <v>28.438218192652801</v>
       </c>
       <c r="F12" t="s">
-        <v>634</v>
+        <v>630</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
@@ -3862,7 +3892,7 @@
         <v>28.375686038828199</v>
       </c>
       <c r="F13" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
@@ -3882,7 +3912,7 @@
         <v>26.824168797592002</v>
       </c>
       <c r="F14" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
@@ -3902,7 +3932,7 @@
         <v>26.672859528649301</v>
       </c>
       <c r="F15" t="s">
-        <v>637</v>
+        <v>633</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
@@ -3922,7 +3952,7 @@
         <v>26.3838421817326</v>
       </c>
       <c r="F16" t="s">
-        <v>638</v>
+        <v>634</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
@@ -3942,7 +3972,7 @@
         <v>26.3346043152597</v>
       </c>
       <c r="F17" t="s">
-        <v>639</v>
+        <v>635</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
@@ -3962,7 +3992,7 @@
         <v>25.8619426800967</v>
       </c>
       <c r="F18" t="s">
-        <v>640</v>
+        <v>636</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
@@ -3982,7 +4012,7 @@
         <v>25.6532043140868</v>
       </c>
       <c r="F19" t="s">
-        <v>641</v>
+        <v>637</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
@@ -4002,7 +4032,7 @@
         <v>25.410464404096601</v>
       </c>
       <c r="F20" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
@@ -4022,7 +4052,7 @@
         <v>24.874491949335901</v>
       </c>
       <c r="F21" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
@@ -4042,7 +4072,7 @@
         <v>24.562965775436901</v>
       </c>
       <c r="F22" t="s">
-        <v>644</v>
+        <v>640</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
@@ -4062,7 +4092,7 @@
         <v>23.524574682404001</v>
       </c>
       <c r="F23" t="s">
-        <v>640</v>
+        <v>636</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
@@ -4082,7 +4112,7 @@
         <v>23.508204317912899</v>
       </c>
       <c r="F24" t="s">
-        <v>645</v>
+        <v>641</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
@@ -4102,7 +4132,7 @@
         <v>22.715238152920499</v>
       </c>
       <c r="F25" t="s">
-        <v>646</v>
+        <v>642</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
@@ -4122,7 +4152,7 @@
         <v>22.602334812785799</v>
       </c>
       <c r="F26" t="s">
-        <v>647</v>
+        <v>643</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
@@ -4142,7 +4172,7 @@
         <v>22.1259801597364</v>
       </c>
       <c r="F27" t="s">
-        <v>648</v>
+        <v>644</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
@@ -4162,7 +4192,7 @@
         <v>21.912102002231901</v>
       </c>
       <c r="F28" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
@@ -4182,7 +4212,7 @@
         <v>21.591462054176901</v>
       </c>
       <c r="F29" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
@@ -4202,7 +4232,7 @@
         <v>21.3960887635677</v>
       </c>
       <c r="F30" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
@@ -4222,7 +4252,7 @@
         <v>21.213238613634399</v>
       </c>
       <c r="F31" t="s">
-        <v>652</v>
+        <v>648</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
@@ -4242,7 +4272,7 @@
         <v>20.8429704254646</v>
       </c>
       <c r="F32" t="s">
-        <v>653</v>
+        <v>649</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
@@ -4262,7 +4292,7 @@
         <v>20.640919027784602</v>
       </c>
       <c r="F33" t="s">
-        <v>654</v>
+        <v>650</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
@@ -4282,7 +4312,7 @@
         <v>20.589801479552701</v>
       </c>
       <c r="F34" t="s">
-        <v>654</v>
+        <v>650</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
@@ -4302,7 +4332,7 @@
         <v>20.5798125651948</v>
       </c>
       <c r="F35" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
@@ -4322,7 +4352,7 @@
         <v>20.476890899019899</v>
       </c>
       <c r="F36" t="s">
-        <v>656</v>
+        <v>652</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
@@ -4342,7 +4372,7 @@
         <v>20.212424633923501</v>
       </c>
       <c r="F37" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
@@ -4362,7 +4392,7 @@
         <v>19.955497586065</v>
       </c>
       <c r="F38" t="s">
-        <v>658</v>
+        <v>654</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
@@ -4382,7 +4412,7 @@
         <v>19.881848870695599</v>
       </c>
       <c r="F39" t="s">
-        <v>659</v>
+        <v>655</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
@@ -4402,7 +4432,7 @@
         <v>19.700276042991302</v>
       </c>
       <c r="F40" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
@@ -4422,7 +4452,7 @@
         <v>19.700276042991302</v>
       </c>
       <c r="F41" t="s">
-        <v>661</v>
+        <v>657</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
@@ -4442,7 +4472,7 @@
         <v>19.3189444642429</v>
       </c>
       <c r="F42" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
@@ -4462,7 +4492,7 @@
         <v>19.186215942509001</v>
       </c>
       <c r="F43" t="s">
-        <v>663</v>
+        <v>659</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
@@ -4482,7 +4512,7 @@
         <v>19.1118210459212</v>
       </c>
       <c r="F44" t="s">
-        <v>664</v>
+        <v>660</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
@@ -4502,7 +4532,7 @@
         <v>19.034001579737801</v>
       </c>
       <c r="F45" t="s">
-        <v>665</v>
+        <v>661</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
@@ -4522,7 +4552,7 @@
         <v>18.972975745334899</v>
       </c>
       <c r="F46" t="s">
-        <v>666</v>
+        <v>662</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
@@ -4542,7 +4572,7 @@
         <v>18.7892429586242</v>
       </c>
       <c r="F47" t="s">
-        <v>667</v>
+        <v>663</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
@@ -4562,7 +4592,7 @@
         <v>18.781514475925299</v>
       </c>
       <c r="F48" t="s">
-        <v>668</v>
+        <v>664</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
@@ -4582,7 +4612,7 @@
         <v>18.672176029421099</v>
       </c>
       <c r="F49" t="s">
-        <v>669</v>
+        <v>665</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
@@ -4602,7 +4632,7 @@
         <v>18.316913942824701</v>
       </c>
       <c r="F50" t="s">
-        <v>670</v>
+        <v>666</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
@@ -4622,7 +4652,7 @@
         <v>18.045036063568499</v>
       </c>
       <c r="F51" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
@@ -4642,7 +4672,7 @@
         <v>18.003601628065098</v>
       </c>
       <c r="F52" t="s">
-        <v>671</v>
+        <v>667</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
@@ -4662,7 +4692,7 @@
         <v>17.996834816492001</v>
       </c>
       <c r="F53" t="s">
-        <v>672</v>
+        <v>668</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
@@ -4682,7 +4712,7 @@
         <v>17.862699659720199</v>
       </c>
       <c r="F54" t="s">
-        <v>673</v>
+        <v>669</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
@@ -4702,7 +4732,7 @@
         <v>17.451921974306401</v>
       </c>
       <c r="F55" t="s">
-        <v>674</v>
+        <v>670</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
@@ -4722,7 +4752,7 @@
         <v>17.381233492496602</v>
       </c>
       <c r="F56" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
@@ -4742,7 +4772,7 @@
         <v>17.233682282979402</v>
       </c>
       <c r="F57" t="s">
-        <v>671</v>
+        <v>667</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
@@ -4762,7 +4792,7 @@
         <v>17.083512077588701</v>
       </c>
       <c r="F58" t="s">
-        <v>676</v>
+        <v>672</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
@@ -4782,7 +4812,7 @@
         <v>17.0774530536669</v>
       </c>
       <c r="F59" t="s">
-        <v>677</v>
+        <v>673</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
@@ -4802,7 +4832,7 @@
         <v>16.778770144225501</v>
       </c>
       <c r="F60" t="s">
-        <v>678</v>
+        <v>674</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
@@ -4822,7 +4852,7 @@
         <v>16.7327476793524</v>
       </c>
       <c r="F61" t="s">
-        <v>679</v>
+        <v>675</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
@@ -4842,7 +4872,7 @@
         <v>16.7207420135354</v>
       </c>
       <c r="F62" t="s">
-        <v>680</v>
+        <v>676</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
@@ -4862,7 +4892,7 @@
         <v>16.578815769508299</v>
       </c>
       <c r="F63" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
@@ -4882,7 +4912,7 @@
         <v>16.450630835547901</v>
       </c>
       <c r="F64" t="s">
-        <v>682</v>
+        <v>678</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
@@ -4902,7 +4932,7 @@
         <v>16.4229116152902</v>
       </c>
       <c r="F65" t="s">
-        <v>683</v>
+        <v>679</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
@@ -4922,7 +4952,7 @@
         <v>16.1898167233302</v>
       </c>
       <c r="F66" t="s">
-        <v>684</v>
+        <v>680</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
@@ -4942,7 +4972,7 @@
         <v>16.0854693710126</v>
       </c>
       <c r="F67" t="s">
-        <v>685</v>
+        <v>681</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
@@ -4962,7 +4992,7 @@
         <v>16.040431538054701</v>
       </c>
       <c r="F68" t="s">
-        <v>686</v>
+        <v>682</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
@@ -4982,7 +5012,7 @@
         <v>15.9712084399298</v>
       </c>
       <c r="F69" t="s">
-        <v>687</v>
+        <v>683</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
@@ -5002,7 +5032,7 @@
         <v>15.919845878305001</v>
       </c>
       <c r="F70" t="s">
-        <v>688</v>
+        <v>684</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
@@ -5022,7 +5052,7 @@
         <v>15.774984955308801</v>
       </c>
       <c r="F71" t="s">
-        <v>689</v>
+        <v>685</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
@@ -5042,7 +5072,7 @@
         <v>15.669704066977999</v>
       </c>
       <c r="F72" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
@@ -5062,7 +5092,7 @@
         <v>15.3929304390788</v>
       </c>
       <c r="F73" t="s">
-        <v>691</v>
+        <v>687</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
@@ -5082,7 +5112,7 @@
         <v>15.3349839632184</v>
       </c>
       <c r="F74" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
@@ -5102,7 +5132,7 @@
         <v>15.2640902165759</v>
       </c>
       <c r="F75" t="s">
-        <v>693</v>
+        <v>689</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
@@ -5122,7 +5152,7 @@
         <v>15.168330523625199</v>
       </c>
       <c r="F76" t="s">
-        <v>694</v>
+        <v>690</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
@@ -5142,7 +5172,7 @@
         <v>15.1615973967172</v>
       </c>
       <c r="F77" t="s">
-        <v>695</v>
+        <v>691</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
@@ -5162,7 +5192,7 @@
         <v>15.1496831871191</v>
       </c>
       <c r="F78" t="s">
-        <v>696</v>
+        <v>692</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
@@ -5182,7 +5212,7 @@
         <v>15.1067311362913</v>
       </c>
       <c r="F79" t="s">
-        <v>697</v>
+        <v>693</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
@@ -5202,7 +5232,7 @@
         <v>14.996134084950199</v>
       </c>
       <c r="F80" t="s">
-        <v>653</v>
+        <v>649</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
@@ -5222,7 +5252,7 @@
         <v>14.842349660869401</v>
       </c>
       <c r="F81" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
@@ -5242,7 +5272,7 @@
         <v>14.7488932574734</v>
       </c>
       <c r="F82" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
@@ -5262,7 +5292,7 @@
         <v>14.583338956552399</v>
       </c>
       <c r="F83" t="s">
-        <v>700</v>
+        <v>696</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
@@ -5282,7 +5312,7 @@
         <v>14.408194254366601</v>
       </c>
       <c r="F84" t="s">
-        <v>701</v>
+        <v>697</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
@@ -5302,7 +5332,7 @@
         <v>14.3137827453408</v>
       </c>
       <c r="F85" t="s">
-        <v>702</v>
+        <v>698</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
@@ -5322,7 +5352,7 @@
         <v>14.2842036679885</v>
       </c>
       <c r="F86" t="s">
-        <v>703</v>
+        <v>699</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.3">
@@ -5342,7 +5372,7 @@
         <v>14.174736943125501</v>
       </c>
       <c r="F87" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
@@ -5362,7 +5392,7 @@
         <v>14.0806334547267</v>
       </c>
       <c r="F88" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
@@ -5382,7 +5412,7 @@
         <v>13.9035058548712</v>
       </c>
       <c r="F89" t="s">
-        <v>703</v>
+        <v>699</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.3">
@@ -5402,7 +5432,7 @@
         <v>13.8956381304464</v>
       </c>
       <c r="F90" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.3">
@@ -5422,7 +5452,7 @@
         <v>13.8781104568586</v>
       </c>
       <c r="F91" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
@@ -5442,7 +5472,7 @@
         <v>13.605268960666701</v>
       </c>
       <c r="F92" t="s">
-        <v>708</v>
+        <v>704</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
@@ -5462,7 +5492,7 @@
         <v>13.485775805123099</v>
       </c>
       <c r="F93" t="s">
-        <v>709</v>
+        <v>705</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
@@ -5482,7 +5512,7 @@
         <v>13.469806295477699</v>
       </c>
       <c r="F94" t="s">
-        <v>710</v>
+        <v>706</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
@@ -5502,7 +5532,7 @@
         <v>13.3107928567999</v>
       </c>
       <c r="F95" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.3">
@@ -5522,7 +5552,7 @@
         <v>13.2690287810385</v>
       </c>
       <c r="F96" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.3">
@@ -5542,7 +5572,7 @@
         <v>13.2161967217259</v>
       </c>
       <c r="F97" t="s">
-        <v>713</v>
+        <v>709</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.3">
@@ -5562,7 +5592,7 @@
         <v>13.2161967217259</v>
       </c>
       <c r="F98" t="s">
-        <v>714</v>
+        <v>710</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.3">
@@ -5582,7 +5612,7 @@
         <v>13.2022898036047</v>
       </c>
       <c r="F99" t="s">
-        <v>715</v>
+        <v>711</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.3">
@@ -5602,7 +5632,7 @@
         <v>13.180325774322499</v>
       </c>
       <c r="F100" t="s">
-        <v>716</v>
+        <v>712</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.3">
@@ -5622,7 +5652,7 @@
         <v>13.157257709737401</v>
       </c>
       <c r="F101" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.3">
@@ -5642,7 +5672,7 @@
         <v>12.7947541623793</v>
       </c>
       <c r="F102" t="s">
-        <v>718</v>
+        <v>714</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.3">
@@ -5662,7 +5692,7 @@
         <v>12.7238109228685</v>
       </c>
       <c r="F103" t="s">
-        <v>719</v>
+        <v>715</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.3">
@@ -5682,7 +5712,7 @@
         <v>12.6373785354898</v>
       </c>
       <c r="F104" t="s">
-        <v>720</v>
+        <v>716</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.3">
@@ -5702,7 +5732,7 @@
         <v>12.6030973251583</v>
       </c>
       <c r="F105" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.3">
@@ -5722,7 +5752,7 @@
         <v>12.600698114401601</v>
       </c>
       <c r="F106" t="s">
-        <v>721</v>
+        <v>717</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.3">
@@ -5742,7 +5772,7 @@
         <v>12.5776386399719</v>
       </c>
       <c r="F107" t="s">
-        <v>722</v>
+        <v>718</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.3">
@@ -5762,7 +5792,7 @@
         <v>12.5419768637166</v>
       </c>
       <c r="F108" t="s">
-        <v>723</v>
+        <v>719</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.3">
@@ -5782,7 +5812,7 @@
         <v>12.176841620941</v>
       </c>
       <c r="F109" t="s">
-        <v>724</v>
+        <v>720</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.3">
@@ -5802,7 +5832,7 @@
         <v>12.097181434883799</v>
       </c>
       <c r="F110" t="s">
-        <v>725</v>
+        <v>721</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.3">
@@ -5822,7 +5852,7 @@
         <v>12.090615535130301</v>
       </c>
       <c r="F111" t="s">
-        <v>726</v>
+        <v>722</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.3">
@@ -5842,7 +5872,7 @@
         <v>12.0716292793362</v>
       </c>
       <c r="F112" t="s">
-        <v>727</v>
+        <v>723</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.3">
@@ -5862,7 +5892,7 @@
         <v>12.065254023216699</v>
       </c>
       <c r="F113" t="s">
-        <v>721</v>
+        <v>717</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.3">
@@ -5882,7 +5912,7 @@
         <v>12.054814724247899</v>
       </c>
       <c r="F114" t="s">
-        <v>728</v>
+        <v>724</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.3">
@@ -5902,7 +5932,7 @@
         <v>12.0136736297812</v>
       </c>
       <c r="F115" t="s">
-        <v>729</v>
+        <v>725</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.3">
@@ -5922,7 +5952,7 @@
         <v>12.0135572938223</v>
       </c>
       <c r="F116" t="s">
-        <v>730</v>
+        <v>726</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.3">
@@ -5942,7 +5972,7 @@
         <v>11.9990585498772</v>
       </c>
       <c r="F117" t="s">
-        <v>729</v>
+        <v>725</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.3">
@@ -5962,7 +5992,7 @@
         <v>11.9584498634764</v>
       </c>
       <c r="F118" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.3">
@@ -5982,7 +6012,7 @@
         <v>11.929929498639099</v>
       </c>
       <c r="F119" t="s">
-        <v>721</v>
+        <v>717</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.3">
@@ -6002,7 +6032,7 @@
         <v>11.7845938678593</v>
       </c>
       <c r="F120" t="s">
-        <v>677</v>
+        <v>673</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.3">
@@ -6022,7 +6052,7 @@
         <v>11.687971369425799</v>
       </c>
       <c r="F121" t="s">
-        <v>732</v>
+        <v>728</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.3">
@@ -6042,7 +6072,7 @@
         <v>11.657863149336499</v>
       </c>
       <c r="F122" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.3">
@@ -6062,7 +6092,7 @@
         <v>11.422342567243</v>
       </c>
       <c r="F123" t="s">
-        <v>733</v>
+        <v>729</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.3">
@@ -6082,7 +6112,7 @@
         <v>11.3774220824378</v>
       </c>
       <c r="F124" t="s">
-        <v>734</v>
+        <v>730</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.3">
@@ -6102,7 +6132,7 @@
         <v>11.3753937878983</v>
       </c>
       <c r="F125" t="s">
-        <v>735</v>
+        <v>731</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.3">
@@ -6122,7 +6152,7 @@
         <v>11.3642884709231</v>
       </c>
       <c r="F126" t="s">
-        <v>736</v>
+        <v>732</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.3">
@@ -6142,7 +6172,7 @@
         <v>11.3576296638368</v>
       </c>
       <c r="F127" t="s">
-        <v>737</v>
+        <v>733</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.3">
@@ -6162,7 +6192,7 @@
         <v>11.326162251538801</v>
       </c>
       <c r="F128" t="s">
-        <v>738</v>
+        <v>734</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.3">
@@ -6182,7 +6212,7 @@
         <v>11.3084382444728</v>
       </c>
       <c r="F129" t="s">
-        <v>739</v>
+        <v>735</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.3">
@@ -6202,7 +6232,7 @@
         <v>11.307430597963</v>
       </c>
       <c r="F130" t="s">
-        <v>723</v>
+        <v>719</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.3">
@@ -6222,7 +6252,7 @@
         <v>11.235835802725999</v>
       </c>
       <c r="F131" t="s">
-        <v>740</v>
+        <v>736</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.3">
@@ -6242,7 +6272,7 @@
         <v>11.1712876004921</v>
       </c>
       <c r="F132" t="s">
-        <v>741</v>
+        <v>737</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.3">
@@ -6262,7 +6292,7 @@
         <v>11.0855266899763</v>
       </c>
       <c r="F133" t="s">
-        <v>742</v>
+        <v>738</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.3">
@@ -6282,7 +6312,7 @@
         <v>11.005066747310501</v>
       </c>
       <c r="F134" t="s">
-        <v>743</v>
+        <v>739</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.3">
@@ -6302,7 +6332,7 @@
         <v>10.9861228866811</v>
       </c>
       <c r="F135" t="s">
-        <v>744</v>
+        <v>740</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.3">
@@ -6322,7 +6352,7 @@
         <v>10.943453068981301</v>
       </c>
       <c r="F136" t="s">
-        <v>745</v>
+        <v>741</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.3">
@@ -6342,7 +6372,7 @@
         <v>10.9267150863036</v>
       </c>
       <c r="F137" t="s">
-        <v>746</v>
+        <v>742</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.3">
@@ -6362,7 +6392,7 @@
         <v>10.886439159538901</v>
       </c>
       <c r="F138" t="s">
-        <v>747</v>
+        <v>743</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.3">
@@ -6382,7 +6412,7 @@
         <v>10.6980024374904</v>
       </c>
       <c r="F139" t="s">
-        <v>748</v>
+        <v>744</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.3">
@@ -6402,7 +6432,7 @@
         <v>10.680748926062501</v>
       </c>
       <c r="F140" t="s">
-        <v>749</v>
+        <v>745</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.3">
@@ -6422,7 +6452,7 @@
         <v>10.6466861094341</v>
       </c>
       <c r="F141" t="s">
-        <v>750</v>
+        <v>746</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.3">
@@ -6442,7 +6472,7 @@
         <v>10.6394691309377</v>
       </c>
       <c r="F142" t="s">
-        <v>751</v>
+        <v>747</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.3">
@@ -6462,7 +6492,7 @@
         <v>10.329914651485399</v>
       </c>
       <c r="F143" t="s">
-        <v>752</v>
+        <v>748</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.3">
@@ -6482,7 +6512,7 @@
         <v>10.2495610755506</v>
       </c>
       <c r="F144" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.3">
@@ -6502,7 +6532,7 @@
         <v>10.1887022585562</v>
       </c>
       <c r="F145" t="s">
-        <v>709</v>
+        <v>705</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.3">
@@ -6522,7 +6552,7 @@
         <v>10.171636606858099</v>
       </c>
       <c r="F146" t="s">
-        <v>754</v>
+        <v>750</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.3">
@@ -6542,7 +6572,7 @@
         <v>10.1397415906265</v>
       </c>
       <c r="F147" t="s">
-        <v>736</v>
+        <v>732</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.3">
@@ -6562,7 +6592,7 @@
         <v>10.121486912939201</v>
       </c>
       <c r="F148" t="s">
-        <v>640</v>
+        <v>636</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.3">
@@ -6582,7 +6612,7 @@
         <v>10.1002181292166</v>
       </c>
       <c r="F149" t="s">
-        <v>744</v>
+        <v>740</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.3">
@@ -6602,7 +6632,7 @@
         <v>10.0532842647957</v>
       </c>
       <c r="F150" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.3">
@@ -6622,7 +6652,7 @@
         <v>10.0507742314113</v>
       </c>
       <c r="F151" t="s">
-        <v>756</v>
+        <v>752</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.3">
@@ -6642,7 +6672,7 @@
         <v>10.0431946505688</v>
       </c>
       <c r="F152" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.3">
@@ -6662,7 +6692,7 @@
         <v>10.033362838030399</v>
       </c>
       <c r="F153" t="s">
-        <v>640</v>
+        <v>636</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.3">
@@ -6682,7 +6712,7 @@
         <v>9.9913910633929692</v>
       </c>
       <c r="F154" t="s">
-        <v>757</v>
+        <v>753</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.3">
@@ -6702,7 +6732,7 @@
         <v>9.9673328397798802</v>
       </c>
       <c r="F155" t="s">
-        <v>758</v>
+        <v>754</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.3">
@@ -6722,7 +6752,7 @@
         <v>9.9543624178760908</v>
       </c>
       <c r="F156" t="s">
-        <v>759</v>
+        <v>755</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.3">
@@ -6742,7 +6772,7 @@
         <v>9.9543624178760908</v>
       </c>
       <c r="F157" t="s">
-        <v>760</v>
+        <v>756</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.3">
@@ -6762,7 +6792,7 @@
         <v>9.9473041601698995</v>
       </c>
       <c r="F158" t="s">
-        <v>761</v>
+        <v>757</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.3">
@@ -6782,7 +6812,7 @@
         <v>9.9413619571784508</v>
       </c>
       <c r="F159" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.3">
@@ -6802,7 +6832,7 @@
         <v>9.8861716933290005</v>
       </c>
       <c r="F160" t="s">
-        <v>763</v>
+        <v>759</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.3">
@@ -6822,7 +6852,7 @@
         <v>9.8686014744254198</v>
       </c>
       <c r="F161" t="s">
-        <v>764</v>
+        <v>760</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.3">
@@ -6842,7 +6872,7 @@
         <v>9.8212735108206601</v>
       </c>
       <c r="F162" t="s">
-        <v>765</v>
+        <v>761</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.3">
@@ -6862,7 +6892,7 @@
         <v>9.8169191057824001</v>
       </c>
       <c r="F163" t="s">
-        <v>766</v>
+        <v>762</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.3">
@@ -6882,7 +6912,7 @@
         <v>9.8073215976236394</v>
       </c>
       <c r="F164" t="s">
-        <v>767</v>
+        <v>763</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.3">
@@ -6902,7 +6932,7 @@
         <v>9.7983727534201108</v>
       </c>
       <c r="F165" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.3">
@@ -6922,7 +6952,7 @@
         <v>9.66095510707129</v>
       </c>
       <c r="F166" t="s">
-        <v>769</v>
+        <v>765</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.3">
@@ -6942,7 +6972,7 @@
         <v>9.5974895117655308</v>
       </c>
       <c r="F167" t="s">
-        <v>770</v>
+        <v>766</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.3">
@@ -6962,7 +6992,7 @@
         <v>9.5886043733806492</v>
       </c>
       <c r="F168" t="s">
-        <v>771</v>
+        <v>767</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.3">
@@ -6982,7 +7012,7 @@
         <v>9.5793890223050298</v>
       </c>
       <c r="F169" t="s">
-        <v>772</v>
+        <v>768</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.3">
@@ -7002,7 +7032,7 @@
         <v>9.5590578994879198</v>
       </c>
       <c r="F170" t="s">
-        <v>773</v>
+        <v>769</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.3">
@@ -7022,7 +7052,7 @@
         <v>9.5260565412073408</v>
       </c>
       <c r="F171" t="s">
-        <v>774</v>
+        <v>770</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.3">
@@ -7042,7 +7072,7 @@
         <v>9.4828238730646603</v>
       </c>
       <c r="F172" t="s">
-        <v>775</v>
+        <v>771</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.3">
@@ -7062,7 +7092,7 @@
         <v>9.4441278749191806</v>
       </c>
       <c r="F173" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.3">
@@ -7082,7 +7112,7 @@
         <v>9.41700809744437</v>
       </c>
       <c r="F174" t="s">
-        <v>777</v>
+        <v>773</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.3">
@@ -7102,7 +7132,7 @@
         <v>9.3903424102422104</v>
       </c>
       <c r="F175" t="s">
-        <v>778</v>
+        <v>774</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.3">
@@ -7122,7 +7152,7 @@
         <v>9.3435913542858504</v>
       </c>
       <c r="F176" t="s">
-        <v>779</v>
+        <v>775</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.3">
@@ -7142,7 +7172,7 @@
         <v>9.1851843700952305</v>
       </c>
       <c r="F177" t="s">
-        <v>665</v>
+        <v>661</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.3">
@@ -7162,7 +7192,7 @@
         <v>9.1726597867806596</v>
       </c>
       <c r="F178" t="s">
-        <v>780</v>
+        <v>776</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.3">
@@ -7182,7 +7212,7 @@
         <v>9.1475520436454794</v>
       </c>
       <c r="F179" t="s">
-        <v>781</v>
+        <v>777</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.3">
@@ -7202,7 +7232,7 @@
         <v>9.1445877796804496</v>
       </c>
       <c r="F180" t="s">
-        <v>782</v>
+        <v>778</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.3">
@@ -7222,7 +7252,7 @@
         <v>9.0792286726436604</v>
       </c>
       <c r="F181" t="s">
-        <v>783</v>
+        <v>779</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.3">
@@ -7242,7 +7272,7 @@
         <v>9.0760000746737504</v>
       </c>
       <c r="F182" t="s">
-        <v>784</v>
+        <v>780</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.3">
@@ -7262,7 +7292,7 @@
         <v>9.0663130946488995</v>
       </c>
       <c r="F183" t="s">
-        <v>785</v>
+        <v>781</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.3">
@@ -7282,7 +7312,7 @@
         <v>8.9970082393929705</v>
       </c>
       <c r="F184" t="s">
-        <v>786</v>
+        <v>782</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.3">
@@ -7302,7 +7332,7 @@
         <v>8.9630454366620391</v>
       </c>
       <c r="F185" t="s">
-        <v>787</v>
+        <v>783</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.3">
@@ -7322,7 +7352,7 @@
         <v>8.8167104919219099</v>
       </c>
       <c r="F186" t="s">
-        <v>788</v>
+        <v>784</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.3">
@@ -7342,7 +7372,7 @@
         <v>8.8068693697684406</v>
       </c>
       <c r="F187" t="s">
-        <v>744</v>
+        <v>740</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.3">
@@ -7362,7 +7392,7 @@
         <v>8.8024451201718499</v>
       </c>
       <c r="F188" t="s">
-        <v>789</v>
+        <v>785</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.3">
@@ -7382,7 +7412,7 @@
         <v>8.7857511864081701</v>
       </c>
       <c r="F189" t="s">
-        <v>790</v>
+        <v>786</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.3">
@@ -7402,7 +7432,7 @@
         <v>8.7397574496245198</v>
       </c>
       <c r="F190" t="s">
-        <v>791</v>
+        <v>787</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.3">
@@ -7422,7 +7452,7 @@
         <v>8.7333862483311808</v>
       </c>
       <c r="F191" t="s">
-        <v>688</v>
+        <v>684</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.3">
@@ -7442,7 +7472,7 @@
         <v>8.6149297898807493</v>
       </c>
       <c r="F192" t="s">
-        <v>756</v>
+        <v>752</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.3">
@@ -7462,7 +7492,7 @@
         <v>8.5845820665692791</v>
       </c>
       <c r="F193" t="s">
-        <v>792</v>
+        <v>788</v>
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.3">
@@ -7482,7 +7512,7 @@
         <v>8.4523158130940406</v>
       </c>
       <c r="F194" t="s">
-        <v>793</v>
+        <v>789</v>
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.3">
@@ -7502,7 +7532,7 @@
         <v>8.3521054416417204</v>
       </c>
       <c r="F195" t="s">
-        <v>794</v>
+        <v>790</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.3">
@@ -7522,7 +7552,7 @@
         <v>8.3473117665259409</v>
       </c>
       <c r="F196" t="s">
-        <v>795</v>
+        <v>791</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.3">
@@ -7542,7 +7572,7 @@
         <v>8.3355703732787898</v>
       </c>
       <c r="F197" t="s">
-        <v>796</v>
+        <v>792</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.3">
@@ -7562,7 +7592,7 @@
         <v>8.3231770025585092</v>
       </c>
       <c r="F198" t="s">
-        <v>797</v>
+        <v>793</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.3">
@@ -7582,7 +7612,7 @@
         <v>8.3127520369808003</v>
       </c>
       <c r="F199" t="s">
-        <v>798</v>
+        <v>794</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.3">
@@ -7602,7 +7632,7 @@
         <v>8.2894415390943408</v>
       </c>
       <c r="F200" t="s">
-        <v>799</v>
+        <v>795</v>
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.3">
@@ -7622,7 +7652,7 @@
         <v>8.2503311048861807</v>
       </c>
       <c r="F201" t="s">
-        <v>800</v>
+        <v>796</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.3">
@@ -7642,7 +7672,7 @@
         <v>8.2350191175959306</v>
       </c>
       <c r="F202" t="s">
-        <v>801</v>
+        <v>797</v>
       </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.3">
@@ -7662,7 +7692,7 @@
         <v>8.1610315376768892</v>
       </c>
       <c r="F203" t="s">
-        <v>688</v>
+        <v>684</v>
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.3">
@@ -7682,7 +7712,7 @@
         <v>8.1018793971675205</v>
       </c>
       <c r="F204" t="s">
-        <v>802</v>
+        <v>798</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.3">
@@ -7702,7 +7732,7 @@
         <v>8.0943047112455595</v>
       </c>
       <c r="F205" t="s">
-        <v>803</v>
+        <v>799</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.3">
@@ -7722,7 +7752,7 @@
         <v>8.0377423719630503</v>
       </c>
       <c r="F206" t="s">
-        <v>792</v>
+        <v>788</v>
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.3">
@@ -7742,7 +7772,7 @@
         <v>7.9852012188942902</v>
       </c>
       <c r="F207" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.3">
@@ -7762,7 +7792,7 @@
         <v>7.9618273718585701</v>
       </c>
       <c r="F208" t="s">
-        <v>805</v>
+        <v>801</v>
       </c>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.3">
@@ -7782,7 +7812,7 @@
         <v>7.9369849980118801</v>
       </c>
       <c r="F209" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.3">
@@ -7802,7 +7832,7 @@
         <v>7.8766041181646198</v>
       </c>
       <c r="F210" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.3">
@@ -7822,7 +7852,7 @@
         <v>7.8483555755187897</v>
       </c>
       <c r="F211" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.3">
@@ -7842,7 +7872,7 @@
         <v>7.8437287598413397</v>
       </c>
       <c r="F212" t="s">
-        <v>807</v>
+        <v>803</v>
       </c>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.3">
@@ -7862,7 +7892,7 @@
         <v>7.8105371765875402</v>
       </c>
       <c r="F213" t="s">
-        <v>808</v>
+        <v>804</v>
       </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.3">
@@ -7882,7 +7912,7 @@
         <v>7.6893367115066198</v>
       </c>
       <c r="F214" t="s">
-        <v>809</v>
+        <v>805</v>
       </c>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.3">
@@ -7902,7 +7932,7 @@
         <v>7.6231234903635299</v>
       </c>
       <c r="F215" t="s">
-        <v>810</v>
+        <v>806</v>
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.3">
@@ -7922,7 +7952,7 @@
         <v>7.6180113138899399</v>
       </c>
       <c r="F216" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.3">
@@ -7942,7 +7972,7 @@
         <v>7.5748012258119202</v>
       </c>
       <c r="F217" t="s">
-        <v>749</v>
+        <v>745</v>
       </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.3">
@@ -7962,7 +7992,7 @@
         <v>7.5660987936497301</v>
       </c>
       <c r="F218" t="s">
-        <v>703</v>
+        <v>699</v>
       </c>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.3">
@@ -7982,7 +8012,7 @@
         <v>7.5069339142187497</v>
       </c>
       <c r="F219" t="s">
-        <v>812</v>
+        <v>808</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.3">
@@ -8002,7 +8032,7 @@
         <v>7.4823473585593101</v>
       </c>
       <c r="F220" t="s">
-        <v>813</v>
+        <v>809</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.3">
@@ -8022,7 +8052,7 @@
         <v>7.4468809564923903</v>
       </c>
       <c r="F221" t="s">
-        <v>814</v>
+        <v>810</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.3">
@@ -8042,7 +8072,7 @@
         <v>7.4320162430043801</v>
       </c>
       <c r="F222" t="s">
-        <v>799</v>
+        <v>795</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.3">
@@ -8062,7 +8092,7 @@
         <v>7.4186898722095398</v>
       </c>
       <c r="F223" t="s">
-        <v>815</v>
+        <v>811</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.3">
@@ -8082,7 +8112,7 @@
         <v>7.4089673934201796</v>
       </c>
       <c r="F224" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.3">
@@ -8102,7 +8132,7 @@
         <v>7.3885723671691004</v>
       </c>
       <c r="F225" t="s">
-        <v>816</v>
+        <v>812</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.3">
@@ -8122,7 +8152,7 @@
         <v>7.3692065703513698</v>
       </c>
       <c r="F226" t="s">
-        <v>817</v>
+        <v>813</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.3">
@@ -8142,7 +8172,7 @@
         <v>7.3658458416664896</v>
       </c>
       <c r="F227" t="s">
-        <v>818</v>
+        <v>814</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.3">
@@ -8162,7 +8192,7 @@
         <v>7.3270197326630599</v>
       </c>
       <c r="F228" t="s">
-        <v>819</v>
+        <v>815</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.3">
@@ -8182,7 +8212,7 @@
         <v>7.3028646551154397</v>
       </c>
       <c r="F229" t="s">
-        <v>820</v>
+        <v>816</v>
       </c>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.3">
@@ -8202,7 +8232,7 @@
         <v>7.2847176028708001</v>
       </c>
       <c r="F230" t="s">
-        <v>703</v>
+        <v>699</v>
       </c>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.3">
@@ -8222,7 +8252,7 @@
         <v>7.24043443158501</v>
       </c>
       <c r="F231" t="s">
-        <v>821</v>
+        <v>817</v>
       </c>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.3">
@@ -8242,7 +8272,7 @@
         <v>7.2287244658529399</v>
       </c>
       <c r="F232" t="s">
-        <v>822</v>
+        <v>818</v>
       </c>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.3">
@@ -8262,7 +8292,7 @@
         <v>7.1479993165243396</v>
       </c>
       <c r="F233" t="s">
-        <v>823</v>
+        <v>819</v>
       </c>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.3">
@@ -8282,7 +8312,7 @@
         <v>7.1433648992877998</v>
       </c>
       <c r="F234" t="s">
-        <v>824</v>
+        <v>820</v>
       </c>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.3">
@@ -8302,7 +8332,7 @@
         <v>7.1432020374203997</v>
       </c>
       <c r="F235" t="s">
-        <v>825</v>
+        <v>821</v>
       </c>
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.3">
@@ -8322,7 +8352,7 @@
         <v>7.1426732683160203</v>
       </c>
       <c r="F236" t="s">
-        <v>826</v>
+        <v>822</v>
       </c>
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.3">
@@ -8342,7 +8372,7 @@
         <v>7.1319138084263001</v>
       </c>
       <c r="F237" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.3">
@@ -8362,7 +8392,7 @@
         <v>7.0912214343747104</v>
       </c>
       <c r="F238" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.3">
@@ -8382,7 +8412,7 @@
         <v>7.0740916250729304</v>
       </c>
       <c r="F239" t="s">
-        <v>827</v>
+        <v>823</v>
       </c>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.3">
@@ -8402,7 +8432,7 @@
         <v>7.06576664497506</v>
       </c>
       <c r="F240" t="s">
-        <v>828</v>
+        <v>824</v>
       </c>
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.3">
@@ -8422,7 +8452,7 @@
         <v>7.05992985303285</v>
       </c>
       <c r="F241" t="s">
-        <v>829</v>
+        <v>825</v>
       </c>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.3">
@@ -8442,7 +8472,7 @@
         <v>7.0273530973057197</v>
       </c>
       <c r="F242" t="s">
-        <v>677</v>
+        <v>673</v>
       </c>
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.3">
@@ -8462,7 +8492,7 @@
         <v>7.0189076386007301</v>
       </c>
       <c r="F243" t="s">
-        <v>830</v>
+        <v>826</v>
       </c>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.3">
@@ -8482,7 +8512,7 @@
         <v>6.99641921803999</v>
       </c>
       <c r="F244" t="s">
-        <v>831</v>
+        <v>827</v>
       </c>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.3">
@@ -8502,7 +8532,7 @@
         <v>6.9800455751615802</v>
       </c>
       <c r="F245" t="s">
-        <v>832</v>
+        <v>828</v>
       </c>
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.3">
@@ -8522,7 +8552,7 @@
         <v>6.9601098820038203</v>
       </c>
       <c r="F246" t="s">
-        <v>833</v>
+        <v>829</v>
       </c>
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.3">
@@ -8542,7 +8572,7 @@
         <v>6.90313828297153</v>
       </c>
       <c r="F247" t="s">
-        <v>658</v>
+        <v>654</v>
       </c>
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.3">
@@ -8562,7 +8592,7 @@
         <v>6.8955198025533804</v>
       </c>
       <c r="F248" t="s">
-        <v>834</v>
+        <v>830</v>
       </c>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.3">
@@ -8582,7 +8612,7 @@
         <v>6.8668171266808598</v>
       </c>
       <c r="F249" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.3">
@@ -8602,7 +8632,7 @@
         <v>6.8611349887950404</v>
       </c>
       <c r="F250" t="s">
-        <v>836</v>
+        <v>832</v>
       </c>
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.3">
@@ -8622,7 +8652,7 @@
         <v>6.7729338967289898</v>
       </c>
       <c r="F251" t="s">
-        <v>837</v>
+        <v>833</v>
       </c>
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.3">
@@ -8642,7 +8672,7 @@
         <v>6.7412351703686904</v>
       </c>
       <c r="F252" t="s">
-        <v>838</v>
+        <v>834</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.3">
@@ -8662,7 +8692,7 @@
         <v>6.73621946206669</v>
       </c>
       <c r="F253" t="s">
-        <v>839</v>
+        <v>835</v>
       </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.3">
@@ -8682,7 +8712,7 @@
         <v>6.7357034970143603</v>
       </c>
       <c r="F254" t="s">
-        <v>840</v>
+        <v>836</v>
       </c>
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.3">
@@ -8702,7 +8732,7 @@
         <v>6.7178791381880103</v>
       </c>
       <c r="F255" t="s">
-        <v>640</v>
+        <v>636</v>
       </c>
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.3">
@@ -8722,7 +8752,7 @@
         <v>6.6760545769181698</v>
       </c>
       <c r="F256" t="s">
-        <v>728</v>
+        <v>724</v>
       </c>
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.3">
@@ -8742,7 +8772,7 @@
         <v>6.5785176623739003</v>
       </c>
       <c r="F257" t="s">
-        <v>841</v>
+        <v>837</v>
       </c>
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.3">
@@ -8762,7 +8792,7 @@
         <v>6.5585300291896296</v>
       </c>
       <c r="F258" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.3">
@@ -8782,7 +8812,7 @@
         <v>6.5583048679177596</v>
       </c>
       <c r="F259" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.3">
@@ -8802,7 +8832,7 @@
         <v>6.5081300923088197</v>
       </c>
       <c r="F260" t="s">
-        <v>843</v>
+        <v>839</v>
       </c>
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.3">
@@ -8822,7 +8852,7 @@
         <v>6.5064477687446001</v>
       </c>
       <c r="F261" t="s">
-        <v>802</v>
+        <v>798</v>
       </c>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.3">
@@ -8842,7 +8872,7 @@
         <v>6.4993587560083999</v>
       </c>
       <c r="F262" t="s">
-        <v>844</v>
+        <v>840</v>
       </c>
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.3">
@@ -8862,7 +8892,7 @@
         <v>6.47817539348328</v>
       </c>
       <c r="F263" t="s">
-        <v>845</v>
+        <v>841</v>
       </c>
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.3">
@@ -8882,7 +8912,7 @@
         <v>6.4764001953892096</v>
       </c>
       <c r="F264" t="s">
-        <v>846</v>
+        <v>842</v>
       </c>
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.3">
@@ -8902,7 +8932,7 @@
         <v>6.4201984904888096</v>
       </c>
       <c r="F265" t="s">
-        <v>847</v>
+        <v>843</v>
       </c>
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.3">
@@ -8922,7 +8952,7 @@
         <v>6.36922147210145</v>
       </c>
       <c r="F266" t="s">
-        <v>848</v>
+        <v>844</v>
       </c>
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.3">
@@ -8942,7 +8972,7 @@
         <v>6.3120473188455097</v>
       </c>
       <c r="F267" t="s">
-        <v>849</v>
+        <v>845</v>
       </c>
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.3">
@@ -8962,7 +8992,7 @@
         <v>6.3007617447694804</v>
       </c>
       <c r="F268" t="s">
-        <v>850</v>
+        <v>846</v>
       </c>
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.3">
@@ -8982,7 +9012,7 @@
         <v>6.2900903590650197</v>
       </c>
       <c r="F269" t="s">
-        <v>640</v>
+        <v>636</v>
       </c>
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.3">
@@ -9002,7 +9032,7 @@
         <v>6.1967465935866599</v>
       </c>
       <c r="F270" t="s">
-        <v>851</v>
+        <v>847</v>
       </c>
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.3">
@@ -9022,7 +9052,7 @@
         <v>6.1936444177675796</v>
       </c>
       <c r="F271" t="s">
-        <v>852</v>
+        <v>848</v>
       </c>
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.3">
@@ -9042,7 +9072,7 @@
         <v>6.1304401057199902</v>
       </c>
       <c r="F272" t="s">
-        <v>853</v>
+        <v>849</v>
       </c>
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.3">
@@ -9062,7 +9092,7 @@
         <v>6.09200180082677</v>
       </c>
       <c r="F273" t="s">
-        <v>779</v>
+        <v>775</v>
       </c>
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.3">
@@ -9082,7 +9112,7 @@
         <v>6.0683833041123902</v>
       </c>
       <c r="F274" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.3">
@@ -9102,7 +9132,7 @@
         <v>6.0408497722887304</v>
       </c>
       <c r="F275" t="s">
-        <v>854</v>
+        <v>850</v>
       </c>
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.3">
@@ -9122,7 +9152,7 @@
         <v>6.0202191297093099</v>
       </c>
       <c r="F276" t="s">
-        <v>855</v>
+        <v>851</v>
       </c>
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.3">
@@ -9142,7 +9172,7 @@
         <v>5.9977986653781601</v>
       </c>
       <c r="F277" t="s">
-        <v>856</v>
+        <v>852</v>
       </c>
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.3">
@@ -9162,7 +9192,7 @@
         <v>5.9556279750532299</v>
       </c>
       <c r="F278" t="s">
-        <v>857</v>
+        <v>853</v>
       </c>
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.3">
@@ -9182,7 +9212,7 @@
         <v>5.9415869721297199</v>
       </c>
       <c r="F279" t="s">
-        <v>858</v>
+        <v>854</v>
       </c>
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.3">
@@ -9202,7 +9232,7 @@
         <v>5.9360999156349097</v>
       </c>
       <c r="F280" t="s">
-        <v>859</v>
+        <v>855</v>
       </c>
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.3">
@@ -9222,7 +9252,7 @@
         <v>5.9338256731312402</v>
       </c>
       <c r="F281" t="s">
-        <v>860</v>
+        <v>856</v>
       </c>
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.3">
@@ -9242,7 +9272,7 @@
         <v>5.8744284196955903</v>
       </c>
       <c r="F282" t="s">
-        <v>861</v>
+        <v>857</v>
       </c>
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.3">
@@ -9262,7 +9292,7 @@
         <v>5.8540220718590303</v>
       </c>
       <c r="F283" t="s">
-        <v>802</v>
+        <v>798</v>
       </c>
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.3">
@@ -9282,7 +9312,7 @@
         <v>5.8521310480324296</v>
       </c>
       <c r="F284" t="s">
-        <v>862</v>
+        <v>858</v>
       </c>
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.3">
@@ -9302,7 +9332,7 @@
         <v>5.8356887568300202</v>
       </c>
       <c r="F285" t="s">
-        <v>668</v>
+        <v>664</v>
       </c>
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.3">
@@ -9322,7 +9352,7 @@
         <v>5.7953837460932602</v>
       </c>
       <c r="F286" t="s">
-        <v>863</v>
+        <v>859</v>
       </c>
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.3">
@@ -9342,7 +9372,7 @@
         <v>5.7863034924084404</v>
       </c>
       <c r="F287" t="s">
-        <v>864</v>
+        <v>860</v>
       </c>
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.3">
@@ -9362,7 +9392,7 @@
         <v>5.7665958313698003</v>
       </c>
       <c r="F288" t="s">
-        <v>865</v>
+        <v>861</v>
       </c>
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.3">
@@ -9382,7 +9412,7 @@
         <v>5.76096268141122</v>
       </c>
       <c r="F289" t="s">
-        <v>866</v>
+        <v>862</v>
       </c>
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.3">
@@ -9402,7 +9432,7 @@
         <v>5.7607246343219103</v>
       </c>
       <c r="F290" t="s">
-        <v>867</v>
+        <v>863</v>
       </c>
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.3">
@@ -9422,7 +9452,7 @@
         <v>5.7505684589115198</v>
       </c>
       <c r="F291" t="s">
-        <v>868</v>
+        <v>864</v>
       </c>
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.3">
@@ -9442,7 +9472,7 @@
         <v>5.7457961924135299</v>
       </c>
       <c r="F292" t="s">
-        <v>869</v>
+        <v>865</v>
       </c>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.3">
@@ -9462,7 +9492,7 @@
         <v>5.7194624376541201</v>
       </c>
       <c r="F293" t="s">
-        <v>870</v>
+        <v>866</v>
       </c>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.3">
@@ -9482,7 +9512,7 @@
         <v>5.71146086730724</v>
       </c>
       <c r="F294" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.3">
@@ -9502,7 +9532,7 @@
         <v>5.6868655717945797</v>
       </c>
       <c r="F295" t="s">
-        <v>661</v>
+        <v>657</v>
       </c>
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.3">
@@ -9522,7 +9552,7 @@
         <v>5.6799193140006201</v>
       </c>
       <c r="F296" t="s">
-        <v>871</v>
+        <v>867</v>
       </c>
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.3">
@@ -9542,7 +9572,7 @@
         <v>5.6570591539654496</v>
       </c>
       <c r="F297" t="s">
-        <v>872</v>
+        <v>868</v>
       </c>
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.3">
@@ -9562,7 +9592,7 @@
         <v>5.6507034655084203</v>
       </c>
       <c r="F298" t="s">
-        <v>873</v>
+        <v>869</v>
       </c>
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.3">
@@ -9582,7 +9612,7 @@
         <v>5.6487388531276297</v>
       </c>
       <c r="F299" t="s">
-        <v>874</v>
+        <v>870</v>
       </c>
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.3">
@@ -9602,7 +9632,7 @@
         <v>5.6465499028300803</v>
       </c>
       <c r="F300" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.3">
@@ -9622,7 +9652,7 @@
         <v>5.6355986161057601</v>
       </c>
       <c r="F301" t="s">
-        <v>876</v>
+        <v>872</v>
       </c>
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.3">
@@ -9642,7 +9672,7 @@
         <v>5.6188647299897498</v>
       </c>
       <c r="F302" t="s">
-        <v>877</v>
+        <v>873</v>
       </c>
     </row>
     <row r="303" spans="1:6" x14ac:dyDescent="0.3">
@@ -9662,7 +9692,7 @@
         <v>5.5978934567913203</v>
       </c>
       <c r="F303" t="s">
-        <v>878</v>
+        <v>874</v>
       </c>
     </row>
     <row r="304" spans="1:6" x14ac:dyDescent="0.3">
@@ -9682,7 +9712,7 @@
         <v>5.5683366094942999</v>
       </c>
       <c r="F304" t="s">
-        <v>879</v>
+        <v>875</v>
       </c>
     </row>
     <row r="305" spans="1:6" x14ac:dyDescent="0.3">
@@ -9702,7 +9732,7 @@
         <v>5.5531164822496502</v>
       </c>
       <c r="F305" t="s">
-        <v>825</v>
+        <v>821</v>
       </c>
     </row>
     <row r="306" spans="1:6" x14ac:dyDescent="0.3">
@@ -9722,7 +9752,7 @@
         <v>5.5357487934304803</v>
       </c>
       <c r="F306" t="s">
-        <v>880</v>
+        <v>876</v>
       </c>
     </row>
     <row r="307" spans="1:6" x14ac:dyDescent="0.3">
@@ -9742,7 +9772,7 @@
         <v>5.4990848719096697</v>
       </c>
       <c r="F307" t="s">
-        <v>881</v>
+        <v>877</v>
       </c>
     </row>
     <row r="308" spans="1:6" x14ac:dyDescent="0.3">
@@ -9762,7 +9792,7 @@
         <v>5.44948807291438</v>
       </c>
       <c r="F308" t="s">
-        <v>785</v>
+        <v>781</v>
       </c>
     </row>
     <row r="309" spans="1:6" x14ac:dyDescent="0.3">
@@ -9782,7 +9812,7 @@
         <v>5.4476747989646297</v>
       </c>
       <c r="F309" t="s">
-        <v>882</v>
+        <v>878</v>
       </c>
     </row>
     <row r="310" spans="1:6" x14ac:dyDescent="0.3">
@@ -9802,7 +9832,7 @@
         <v>5.3962552353462199</v>
       </c>
       <c r="F310" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="311" spans="1:6" x14ac:dyDescent="0.3">
@@ -9822,7 +9852,7 @@
         <v>5.3700176378374103</v>
       </c>
       <c r="F311" t="s">
-        <v>884</v>
+        <v>880</v>
       </c>
     </row>
     <row r="312" spans="1:6" x14ac:dyDescent="0.3">
@@ -9842,7 +9872,7 @@
         <v>5.3677999735550399</v>
       </c>
       <c r="F312" t="s">
-        <v>784</v>
+        <v>780</v>
       </c>
     </row>
     <row r="313" spans="1:6" x14ac:dyDescent="0.3">
@@ -9862,7 +9892,7 @@
         <v>5.3656149852126296</v>
       </c>
       <c r="F313" t="s">
-        <v>885</v>
+        <v>881</v>
       </c>
     </row>
     <row r="314" spans="1:6" x14ac:dyDescent="0.3">
@@ -9882,7 +9912,7 @@
         <v>5.3499190005509902</v>
       </c>
       <c r="F314" t="s">
-        <v>688</v>
+        <v>684</v>
       </c>
     </row>
     <row r="315" spans="1:6" x14ac:dyDescent="0.3">
@@ -9902,7 +9932,7 @@
         <v>5.3272773836448399</v>
       </c>
       <c r="F315" t="s">
-        <v>886</v>
+        <v>882</v>
       </c>
     </row>
     <row r="316" spans="1:6" x14ac:dyDescent="0.3">
@@ -9922,7 +9952,7 @@
         <v>5.3192601869810199</v>
       </c>
       <c r="F316" t="s">
-        <v>887</v>
+        <v>883</v>
       </c>
     </row>
     <row r="317" spans="1:6" x14ac:dyDescent="0.3">
@@ -9942,7 +9972,7 @@
         <v>5.2891308896034204</v>
       </c>
       <c r="F317" t="s">
-        <v>668</v>
+        <v>664</v>
       </c>
     </row>
     <row r="318" spans="1:6" x14ac:dyDescent="0.3">
@@ -9962,7 +9992,7 @@
         <v>5.2508709334376196</v>
       </c>
       <c r="F318" t="s">
-        <v>888</v>
+        <v>884</v>
       </c>
     </row>
     <row r="319" spans="1:6" x14ac:dyDescent="0.3">
@@ -9982,7 +10012,7 @@
         <v>5.2400518036661303</v>
       </c>
       <c r="F319" t="s">
-        <v>889</v>
+        <v>885</v>
       </c>
     </row>
     <row r="320" spans="1:6" x14ac:dyDescent="0.3">
@@ -10002,7 +10032,7 @@
         <v>5.2261454319473204</v>
       </c>
       <c r="F320" t="s">
-        <v>890</v>
+        <v>886</v>
       </c>
     </row>
     <row r="321" spans="1:6" x14ac:dyDescent="0.3">
@@ -10022,7 +10052,7 @@
         <v>5.1988570420955504</v>
       </c>
       <c r="F321" t="s">
-        <v>891</v>
+        <v>887</v>
       </c>
     </row>
     <row r="322" spans="1:6" x14ac:dyDescent="0.3">
@@ -10042,7 +10072,7 @@
         <v>5.0801979900216798</v>
       </c>
       <c r="F322" t="s">
-        <v>892</v>
+        <v>888</v>
       </c>
     </row>
     <row r="323" spans="1:6" x14ac:dyDescent="0.3">
@@ -10062,7 +10092,7 @@
         <v>5.0533432003168999</v>
       </c>
       <c r="F323" t="s">
-        <v>773</v>
+        <v>769</v>
       </c>
     </row>
     <row r="324" spans="1:6" x14ac:dyDescent="0.3">
@@ -10082,7 +10112,7 @@
         <v>5.0518841987690699</v>
       </c>
       <c r="F324" t="s">
-        <v>893</v>
+        <v>889</v>
       </c>
     </row>
     <row r="325" spans="1:6" x14ac:dyDescent="0.3">
@@ -10102,7 +10132,7 @@
         <v>4.9803930802488496</v>
       </c>
       <c r="F325" t="s">
-        <v>833</v>
+        <v>829</v>
       </c>
     </row>
     <row r="326" spans="1:6" x14ac:dyDescent="0.3">
@@ -10122,7 +10152,7 @@
         <v>4.9469140340737399</v>
       </c>
       <c r="F326" t="s">
-        <v>887</v>
+        <v>883</v>
       </c>
     </row>
     <row r="327" spans="1:6" x14ac:dyDescent="0.3">
@@ -10142,7 +10172,7 @@
         <v>4.9395370747425504</v>
       </c>
       <c r="F327" t="s">
-        <v>703</v>
+        <v>699</v>
       </c>
     </row>
     <row r="328" spans="1:6" x14ac:dyDescent="0.3">
@@ -10162,7 +10192,7 @@
         <v>4.9363261204278297</v>
       </c>
       <c r="F328" t="s">
-        <v>894</v>
+        <v>890</v>
       </c>
     </row>
     <row r="329" spans="1:6" x14ac:dyDescent="0.3">
@@ -10182,7 +10212,7 @@
         <v>4.8752779203898102</v>
       </c>
       <c r="F329" t="s">
-        <v>696</v>
+        <v>692</v>
       </c>
     </row>
     <row r="330" spans="1:6" x14ac:dyDescent="0.3">
@@ -10202,7 +10232,7 @@
         <v>4.8489222301028203</v>
       </c>
       <c r="F330" t="s">
-        <v>895</v>
+        <v>891</v>
       </c>
     </row>
     <row r="331" spans="1:6" x14ac:dyDescent="0.3">
@@ -10222,7 +10252,7 @@
         <v>4.8108119852551203</v>
       </c>
       <c r="F331" t="s">
-        <v>833</v>
+        <v>829</v>
       </c>
     </row>
     <row r="332" spans="1:6" x14ac:dyDescent="0.3">
@@ -10242,7 +10272,7 @@
         <v>4.7780583698138299</v>
       </c>
       <c r="F332" t="s">
-        <v>828</v>
+        <v>824</v>
       </c>
     </row>
     <row r="333" spans="1:6" x14ac:dyDescent="0.3">
@@ -10262,7 +10292,7 @@
         <v>4.7551946726561001</v>
       </c>
       <c r="F333" t="s">
-        <v>825</v>
+        <v>821</v>
       </c>
     </row>
     <row r="334" spans="1:6" x14ac:dyDescent="0.3">
@@ -10282,7 +10312,7 @@
         <v>4.7487227226827997</v>
       </c>
       <c r="F334" t="s">
-        <v>739</v>
+        <v>735</v>
       </c>
     </row>
     <row r="335" spans="1:6" x14ac:dyDescent="0.3">
@@ -10302,7 +10332,7 @@
         <v>4.7416980164540501</v>
       </c>
       <c r="F335" t="s">
-        <v>896</v>
+        <v>892</v>
       </c>
     </row>
     <row r="336" spans="1:6" x14ac:dyDescent="0.3">
@@ -10322,7 +10352,7 @@
         <v>4.7321939103357504</v>
       </c>
       <c r="F336" t="s">
-        <v>813</v>
+        <v>809</v>
       </c>
     </row>
     <row r="337" spans="1:6" x14ac:dyDescent="0.3">
@@ -10342,7 +10372,7 @@
         <v>4.71553653889399</v>
       </c>
       <c r="F337" t="s">
-        <v>897</v>
+        <v>893</v>
       </c>
     </row>
     <row r="338" spans="1:6" x14ac:dyDescent="0.3">
@@ -10362,7 +10392,7 @@
         <v>4.6897225279282502</v>
       </c>
       <c r="F338" t="s">
-        <v>748</v>
+        <v>744</v>
       </c>
     </row>
     <row r="339" spans="1:6" x14ac:dyDescent="0.3">
@@ -10382,7 +10412,7 @@
         <v>4.6589850918279403</v>
       </c>
       <c r="F339" t="s">
-        <v>898</v>
+        <v>894</v>
       </c>
     </row>
     <row r="340" spans="1:6" x14ac:dyDescent="0.3">
@@ -10402,7 +10432,7 @@
         <v>4.6324796551989103</v>
       </c>
       <c r="F340" t="s">
-        <v>899</v>
+        <v>895</v>
       </c>
     </row>
     <row r="341" spans="1:6" x14ac:dyDescent="0.3">
@@ -10422,7 +10452,7 @@
         <v>4.6281634939169596</v>
       </c>
       <c r="F341" t="s">
-        <v>900</v>
+        <v>896</v>
       </c>
     </row>
     <row r="342" spans="1:6" x14ac:dyDescent="0.3">
@@ -10442,7 +10472,7 @@
         <v>4.6248849506470897</v>
       </c>
       <c r="F342" t="s">
-        <v>901</v>
+        <v>897</v>
       </c>
     </row>
     <row r="343" spans="1:6" x14ac:dyDescent="0.3">
@@ -10462,7 +10492,7 @@
         <v>4.6241056690485696</v>
       </c>
       <c r="F343" t="s">
-        <v>902</v>
+        <v>898</v>
       </c>
     </row>
     <row r="344" spans="1:6" x14ac:dyDescent="0.3">
@@ -10482,7 +10512,7 @@
         <v>4.5811308494089102</v>
       </c>
       <c r="F344" t="s">
-        <v>903</v>
+        <v>899</v>
       </c>
     </row>
     <row r="345" spans="1:6" x14ac:dyDescent="0.3">
@@ -10502,7 +10532,7 @@
         <v>4.5635639307285603</v>
       </c>
       <c r="F345" t="s">
-        <v>833</v>
+        <v>829</v>
       </c>
     </row>
     <row r="346" spans="1:6" x14ac:dyDescent="0.3">
@@ -10522,7 +10552,7 @@
         <v>4.5375851846233699</v>
       </c>
       <c r="F346" t="s">
-        <v>703</v>
+        <v>699</v>
       </c>
     </row>
     <row r="347" spans="1:6" x14ac:dyDescent="0.3">
@@ -10542,7 +10572,7 @@
         <v>4.5017060801405302</v>
       </c>
       <c r="F347" t="s">
-        <v>904</v>
+        <v>900</v>
       </c>
     </row>
     <row r="348" spans="1:6" x14ac:dyDescent="0.3">
@@ -10562,7 +10592,7 @@
         <v>4.4924297549207104</v>
       </c>
       <c r="F348" t="s">
-        <v>905</v>
+        <v>901</v>
       </c>
     </row>
     <row r="349" spans="1:6" x14ac:dyDescent="0.3">
@@ -10582,7 +10612,7 @@
         <v>4.4683218881485498</v>
       </c>
       <c r="F349" t="s">
-        <v>906</v>
+        <v>902</v>
       </c>
     </row>
     <row r="350" spans="1:6" x14ac:dyDescent="0.3">
@@ -10602,7 +10632,7 @@
         <v>4.4460445451803698</v>
       </c>
       <c r="F350" t="s">
-        <v>907</v>
+        <v>903</v>
       </c>
     </row>
     <row r="351" spans="1:6" x14ac:dyDescent="0.3">
@@ -10622,7 +10652,7 @@
         <v>4.4087349296972</v>
       </c>
       <c r="F351" t="s">
-        <v>701</v>
+        <v>697</v>
       </c>
     </row>
     <row r="352" spans="1:6" x14ac:dyDescent="0.3">
@@ -10642,7 +10672,7 @@
         <v>4.3396995207840598</v>
       </c>
       <c r="F352" t="s">
-        <v>908</v>
+        <v>904</v>
       </c>
     </row>
     <row r="353" spans="1:6" x14ac:dyDescent="0.3">
@@ -10662,7 +10692,7 @@
         <v>4.3362837612531901</v>
       </c>
       <c r="F353" t="s">
-        <v>889</v>
+        <v>885</v>
       </c>
     </row>
     <row r="354" spans="1:6" x14ac:dyDescent="0.3">
@@ -10682,7 +10712,7 @@
         <v>4.3323417960261503</v>
       </c>
       <c r="F354" t="s">
-        <v>909</v>
+        <v>905</v>
       </c>
     </row>
     <row r="355" spans="1:6" x14ac:dyDescent="0.3">
@@ -10702,7 +10732,7 @@
         <v>4.3304738036856403</v>
       </c>
       <c r="F355" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
     </row>
     <row r="356" spans="1:6" x14ac:dyDescent="0.3">
@@ -10722,7 +10752,7 @@
         <v>4.3254613188698698</v>
       </c>
       <c r="F356" t="s">
-        <v>911</v>
+        <v>907</v>
       </c>
     </row>
     <row r="357" spans="1:6" x14ac:dyDescent="0.3">
@@ -10742,7 +10772,7 @@
         <v>4.3254613188698698</v>
       </c>
       <c r="F357" t="s">
-        <v>912</v>
+        <v>908</v>
       </c>
     </row>
     <row r="358" spans="1:6" x14ac:dyDescent="0.3">
@@ -10762,7 +10792,7 @@
         <v>4.3224101657762501</v>
       </c>
       <c r="F358" t="s">
-        <v>913</v>
+        <v>909</v>
       </c>
     </row>
     <row r="359" spans="1:6" x14ac:dyDescent="0.3">
@@ -10782,7 +10812,7 @@
         <v>4.3207566079005097</v>
       </c>
       <c r="F359" t="s">
-        <v>914</v>
+        <v>910</v>
       </c>
     </row>
     <row r="360" spans="1:6" x14ac:dyDescent="0.3">
@@ -10802,7 +10832,7 @@
         <v>4.2967801475052498</v>
       </c>
       <c r="F360" t="s">
-        <v>802</v>
+        <v>798</v>
       </c>
     </row>
     <row r="361" spans="1:6" x14ac:dyDescent="0.3">
@@ -10822,7 +10852,7 @@
         <v>4.2840709705767299</v>
       </c>
       <c r="F361" t="s">
-        <v>915</v>
+        <v>911</v>
       </c>
     </row>
     <row r="362" spans="1:6" x14ac:dyDescent="0.3">
@@ -10842,7 +10872,7 @@
         <v>4.1976799337289803</v>
       </c>
       <c r="F362" t="s">
-        <v>916</v>
+        <v>912</v>
       </c>
     </row>
     <row r="363" spans="1:6" x14ac:dyDescent="0.3">
@@ -10862,7 +10892,7 @@
         <v>4.1706732469325498</v>
       </c>
       <c r="F363" t="s">
-        <v>746</v>
+        <v>742</v>
       </c>
     </row>
     <row r="364" spans="1:6" x14ac:dyDescent="0.3">
@@ -10882,7 +10912,7 @@
         <v>4.1617012843110501</v>
       </c>
       <c r="F364" t="s">
-        <v>703</v>
+        <v>699</v>
       </c>
     </row>
     <row r="365" spans="1:6" x14ac:dyDescent="0.3">
@@ -10902,7 +10932,7 @@
         <v>4.1559519644161904</v>
       </c>
       <c r="F365" t="s">
-        <v>744</v>
+        <v>740</v>
       </c>
     </row>
     <row r="366" spans="1:6" x14ac:dyDescent="0.3">
@@ -10922,7 +10952,7 @@
         <v>4.1475840662413299</v>
       </c>
       <c r="F366" t="s">
-        <v>640</v>
+        <v>636</v>
       </c>
     </row>
     <row r="367" spans="1:6" x14ac:dyDescent="0.3">
@@ -10942,7 +10972,7 @@
         <v>4.1324963281864804</v>
       </c>
       <c r="F367" t="s">
-        <v>917</v>
+        <v>913</v>
       </c>
     </row>
     <row r="368" spans="1:6" x14ac:dyDescent="0.3">
@@ -10962,7 +10992,7 @@
         <v>4.1163291783837996</v>
       </c>
       <c r="F368" t="s">
-        <v>918</v>
+        <v>914</v>
       </c>
     </row>
     <row r="369" spans="1:6" x14ac:dyDescent="0.3">
@@ -10982,7 +11012,7 @@
         <v>4.09390160729874</v>
       </c>
       <c r="F369" t="s">
-        <v>919</v>
+        <v>915</v>
       </c>
     </row>
     <row r="370" spans="1:6" x14ac:dyDescent="0.3">
@@ -11002,7 +11032,7 @@
         <v>4.0636369884159302</v>
       </c>
       <c r="F370" t="s">
-        <v>736</v>
+        <v>732</v>
       </c>
     </row>
     <row r="371" spans="1:6" x14ac:dyDescent="0.3">
@@ -11022,7 +11052,7 @@
         <v>4.0343984656052303</v>
       </c>
       <c r="F371" t="s">
-        <v>771</v>
+        <v>767</v>
       </c>
     </row>
     <row r="372" spans="1:6" x14ac:dyDescent="0.3">
@@ -11042,7 +11072,7 @@
         <v>4.02819348258374</v>
       </c>
       <c r="F372" t="s">
-        <v>920</v>
+        <v>916</v>
       </c>
     </row>
     <row r="373" spans="1:6" x14ac:dyDescent="0.3">
@@ -11062,7 +11092,7 @@
         <v>3.9945162741770801</v>
       </c>
       <c r="F373" t="s">
-        <v>921</v>
+        <v>917</v>
       </c>
     </row>
     <row r="374" spans="1:6" x14ac:dyDescent="0.3">
@@ -11082,7 +11112,7 @@
         <v>3.9730955895742799</v>
       </c>
       <c r="F374" t="s">
-        <v>922</v>
+        <v>918</v>
       </c>
     </row>
     <row r="375" spans="1:6" x14ac:dyDescent="0.3">
@@ -11102,7 +11132,7 @@
         <v>3.9318256327243302</v>
       </c>
       <c r="F375" t="s">
-        <v>923</v>
+        <v>919</v>
       </c>
     </row>
     <row r="376" spans="1:6" x14ac:dyDescent="0.3">
@@ -11122,7 +11152,7 @@
         <v>3.9121250410386601</v>
       </c>
       <c r="F376" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
     </row>
     <row r="377" spans="1:6" x14ac:dyDescent="0.3">
@@ -11142,7 +11172,7 @@
         <v>3.90080213621121</v>
       </c>
       <c r="F377" t="s">
-        <v>925</v>
+        <v>921</v>
       </c>
     </row>
     <row r="378" spans="1:6" x14ac:dyDescent="0.3">
@@ -11162,7 +11192,7 @@
         <v>3.81889788850359</v>
       </c>
       <c r="F378" t="s">
-        <v>926</v>
+        <v>922</v>
       </c>
     </row>
     <row r="379" spans="1:6" x14ac:dyDescent="0.3">
@@ -11182,7 +11212,7 @@
         <v>3.8063155397104902</v>
       </c>
       <c r="F379" t="s">
-        <v>812</v>
+        <v>808</v>
       </c>
     </row>
     <row r="380" spans="1:6" x14ac:dyDescent="0.3">
@@ -11202,7 +11232,7 @@
         <v>3.78266526676145</v>
       </c>
       <c r="F380" t="s">
-        <v>927</v>
+        <v>923</v>
       </c>
     </row>
     <row r="381" spans="1:6" x14ac:dyDescent="0.3">
@@ -11222,7 +11252,7 @@
         <v>3.7749925564429301</v>
       </c>
       <c r="F381" t="s">
-        <v>802</v>
+        <v>798</v>
       </c>
     </row>
     <row r="382" spans="1:6" x14ac:dyDescent="0.3">
@@ -11242,7 +11272,7 @@
         <v>3.7727609380946401</v>
       </c>
       <c r="F382" t="s">
-        <v>928</v>
+        <v>924</v>
       </c>
     </row>
     <row r="383" spans="1:6" x14ac:dyDescent="0.3">
@@ -11262,7 +11292,7 @@
         <v>3.7603189083458801</v>
       </c>
       <c r="F383" t="s">
-        <v>929</v>
+        <v>925</v>
       </c>
     </row>
     <row r="384" spans="1:6" x14ac:dyDescent="0.3">
@@ -11282,7 +11312,7 @@
         <v>3.74360435380318</v>
       </c>
       <c r="F384" t="s">
-        <v>930</v>
+        <v>926</v>
       </c>
     </row>
     <row r="385" spans="1:6" x14ac:dyDescent="0.3">
@@ -11302,7 +11332,7 @@
         <v>3.7358727575227002</v>
       </c>
       <c r="F385" t="s">
-        <v>931</v>
+        <v>927</v>
       </c>
     </row>
     <row r="386" spans="1:6" x14ac:dyDescent="0.3">
@@ -11322,7 +11352,7 @@
         <v>3.6824343159349202</v>
       </c>
       <c r="F386" t="s">
-        <v>932</v>
+        <v>928</v>
       </c>
     </row>
     <row r="387" spans="1:6" x14ac:dyDescent="0.3">
@@ -11342,7 +11372,7 @@
         <v>3.65566210917933</v>
       </c>
       <c r="F387" t="s">
-        <v>870</v>
+        <v>866</v>
       </c>
     </row>
     <row r="388" spans="1:6" x14ac:dyDescent="0.3">
@@ -11362,7 +11392,7 @@
         <v>3.6330968881166799</v>
       </c>
       <c r="F388" t="s">
-        <v>873</v>
+        <v>869</v>
       </c>
     </row>
     <row r="389" spans="1:6" x14ac:dyDescent="0.3">
@@ -11382,7 +11412,7 @@
         <v>3.61546407517063</v>
       </c>
       <c r="F389" t="s">
-        <v>933</v>
+        <v>929</v>
       </c>
     </row>
     <row r="390" spans="1:6" x14ac:dyDescent="0.3">
@@ -11402,7 +11432,7 @@
         <v>3.60036493431268</v>
       </c>
       <c r="F390" t="s">
-        <v>934</v>
+        <v>930</v>
       </c>
     </row>
     <row r="391" spans="1:6" x14ac:dyDescent="0.3">
@@ -11422,7 +11452,7 @@
         <v>3.5904393813006799</v>
       </c>
       <c r="F391" t="s">
-        <v>879</v>
+        <v>875</v>
       </c>
     </row>
     <row r="392" spans="1:6" x14ac:dyDescent="0.3">
@@ -11442,7 +11472,7 @@
         <v>3.5523495762771602</v>
       </c>
       <c r="F392" t="s">
-        <v>935</v>
+        <v>931</v>
       </c>
     </row>
     <row r="393" spans="1:6" x14ac:dyDescent="0.3">
@@ -11462,7 +11492,7 @@
         <v>3.5377287914615998</v>
       </c>
       <c r="F393" t="s">
-        <v>936</v>
+        <v>932</v>
       </c>
     </row>
     <row r="394" spans="1:6" x14ac:dyDescent="0.3">
@@ -11482,7 +11512,7 @@
         <v>3.53156796564959</v>
       </c>
       <c r="F394" t="s">
-        <v>937</v>
+        <v>933</v>
       </c>
     </row>
     <row r="395" spans="1:6" x14ac:dyDescent="0.3">
@@ -11502,7 +11532,7 @@
         <v>3.5282158757950901</v>
       </c>
       <c r="F395" t="s">
-        <v>792</v>
+        <v>788</v>
       </c>
     </row>
     <row r="396" spans="1:6" x14ac:dyDescent="0.3">
@@ -11522,7 +11552,7 @@
         <v>3.5163969116407801</v>
       </c>
       <c r="F396" t="s">
-        <v>938</v>
+        <v>934</v>
       </c>
     </row>
     <row r="397" spans="1:6" x14ac:dyDescent="0.3">
@@ -11542,7 +11572,7 @@
         <v>3.47095915403087</v>
       </c>
       <c r="F397" t="s">
-        <v>939</v>
+        <v>935</v>
       </c>
     </row>
     <row r="398" spans="1:6" x14ac:dyDescent="0.3">
@@ -11562,7 +11592,7 @@
         <v>3.4682184794634199</v>
       </c>
       <c r="F398" t="s">
-        <v>940</v>
+        <v>936</v>
       </c>
     </row>
     <row r="399" spans="1:6" x14ac:dyDescent="0.3">
@@ -11582,7 +11612,7 @@
         <v>3.4629788249822302</v>
       </c>
       <c r="F399" t="s">
-        <v>668</v>
+        <v>664</v>
       </c>
     </row>
     <row r="400" spans="1:6" x14ac:dyDescent="0.3">
@@ -11602,7 +11632,7 @@
         <v>3.4622494827211399</v>
       </c>
       <c r="F400" t="s">
-        <v>941</v>
+        <v>937</v>
       </c>
     </row>
     <row r="401" spans="1:6" x14ac:dyDescent="0.3">
@@ -11622,7 +11652,7 @@
         <v>3.4583201899326901</v>
       </c>
       <c r="F401" t="s">
-        <v>942</v>
+        <v>938</v>
       </c>
     </row>
     <row r="402" spans="1:6" x14ac:dyDescent="0.3">
@@ -11642,7 +11672,7 @@
         <v>3.4327609021518999</v>
       </c>
       <c r="F402" t="s">
-        <v>829</v>
+        <v>825</v>
       </c>
     </row>
     <row r="403" spans="1:6" x14ac:dyDescent="0.3">
@@ -11662,7 +11692,7 @@
         <v>3.40191155013177</v>
       </c>
       <c r="F403" t="s">
-        <v>943</v>
+        <v>939</v>
       </c>
     </row>
     <row r="404" spans="1:6" x14ac:dyDescent="0.3">
@@ -11682,7 +11712,7 @@
         <v>3.36220570062344</v>
       </c>
       <c r="F404" t="s">
-        <v>944</v>
+        <v>940</v>
       </c>
     </row>
     <row r="405" spans="1:6" x14ac:dyDescent="0.3">
@@ -11702,7 +11732,7 @@
         <v>3.34823184847725</v>
       </c>
       <c r="F405" t="s">
-        <v>945</v>
+        <v>941</v>
       </c>
     </row>
     <row r="406" spans="1:6" x14ac:dyDescent="0.3">
@@ -11722,7 +11752,7 @@
         <v>3.3355511833954798</v>
       </c>
       <c r="F406" t="s">
-        <v>946</v>
+        <v>942</v>
       </c>
     </row>
     <row r="407" spans="1:6" x14ac:dyDescent="0.3">
@@ -11742,7 +11772,7 @@
         <v>3.3297353844779698</v>
       </c>
       <c r="F407" t="s">
-        <v>940</v>
+        <v>936</v>
       </c>
     </row>
     <row r="408" spans="1:6" x14ac:dyDescent="0.3">
@@ -11762,7 +11792,7 @@
         <v>3.3289524747888302</v>
       </c>
       <c r="F408" t="s">
-        <v>658</v>
+        <v>654</v>
       </c>
     </row>
     <row r="409" spans="1:6" x14ac:dyDescent="0.3">
@@ -11782,7 +11812,7 @@
         <v>3.3174976099247901</v>
       </c>
       <c r="F409" t="s">
-        <v>897</v>
+        <v>893</v>
       </c>
     </row>
     <row r="410" spans="1:6" x14ac:dyDescent="0.3">
@@ -11802,7 +11832,7 @@
         <v>3.3099813733904901</v>
       </c>
       <c r="F410" t="s">
-        <v>947</v>
+        <v>943</v>
       </c>
     </row>
     <row r="411" spans="1:6" x14ac:dyDescent="0.3">
@@ -11822,7 +11852,7 @@
         <v>3.29583686600433</v>
       </c>
       <c r="F411" t="s">
-        <v>948</v>
+        <v>944</v>
       </c>
     </row>
     <row r="412" spans="1:6" x14ac:dyDescent="0.3">
@@ -11842,7 +11872,7 @@
         <v>3.2609663084404898</v>
       </c>
       <c r="F412" t="s">
-        <v>773</v>
+        <v>769</v>
       </c>
     </row>
     <row r="413" spans="1:6" x14ac:dyDescent="0.3">
@@ -11862,7 +11892,7 @@
         <v>3.2608648189155902</v>
       </c>
       <c r="F413" t="s">
-        <v>949</v>
+        <v>945</v>
       </c>
     </row>
     <row r="414" spans="1:6" x14ac:dyDescent="0.3">
@@ -11882,7 +11912,7 @@
         <v>3.2392900581547899</v>
       </c>
       <c r="F414" t="s">
-        <v>950</v>
+        <v>946</v>
       </c>
     </row>
     <row r="415" spans="1:6" x14ac:dyDescent="0.3">
@@ -11902,7 +11932,7 @@
         <v>3.23501549458478</v>
       </c>
       <c r="F415" t="s">
-        <v>877</v>
+        <v>873</v>
       </c>
     </row>
     <row r="416" spans="1:6" x14ac:dyDescent="0.3">
@@ -11922,7 +11952,7 @@
         <v>3.20827700274473</v>
       </c>
       <c r="F416" t="s">
-        <v>951</v>
+        <v>947</v>
       </c>
     </row>
     <row r="417" spans="1:6" x14ac:dyDescent="0.3">
@@ -11942,7 +11972,7 @@
         <v>3.20808284986897</v>
       </c>
       <c r="F417" t="s">
-        <v>898</v>
+        <v>894</v>
       </c>
     </row>
     <row r="418" spans="1:6" x14ac:dyDescent="0.3">
@@ -11962,7 +11992,7 @@
         <v>3.2011509491062502</v>
       </c>
       <c r="F418" t="s">
-        <v>952</v>
+        <v>948</v>
       </c>
     </row>
     <row r="419" spans="1:6" x14ac:dyDescent="0.3">
@@ -11982,7 +12012,7 @@
         <v>3.1921827203040101</v>
       </c>
       <c r="F419" t="s">
-        <v>953</v>
+        <v>949</v>
       </c>
     </row>
     <row r="420" spans="1:6" x14ac:dyDescent="0.3">
@@ -12002,7 +12032,7 @@
         <v>3.19058553639747</v>
       </c>
       <c r="F420" t="s">
-        <v>954</v>
+        <v>950</v>
       </c>
     </row>
     <row r="421" spans="1:6" x14ac:dyDescent="0.3">
@@ -12022,7 +12052,7 @@
         <v>3.1832486472250499</v>
       </c>
       <c r="F421" t="s">
-        <v>955</v>
+        <v>951</v>
       </c>
     </row>
     <row r="422" spans="1:6" x14ac:dyDescent="0.3">
@@ -12042,7 +12072,7 @@
         <v>3.1739301131640798</v>
       </c>
       <c r="F422" t="s">
-        <v>680</v>
+        <v>676</v>
       </c>
     </row>
     <row r="423" spans="1:6" x14ac:dyDescent="0.3">
@@ -12062,7 +12092,7 @@
         <v>3.1735908713686798</v>
       </c>
       <c r="F423" t="s">
-        <v>774</v>
+        <v>770</v>
       </c>
     </row>
     <row r="424" spans="1:6" x14ac:dyDescent="0.3">
@@ -12082,7 +12112,7 @@
         <v>3.1719315978584501</v>
       </c>
       <c r="F424" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
     </row>
     <row r="425" spans="1:6" x14ac:dyDescent="0.3">
@@ -12102,7 +12132,7 @@
         <v>3.1703165511163398</v>
       </c>
       <c r="F425" t="s">
-        <v>739</v>
+        <v>735</v>
       </c>
     </row>
     <row r="426" spans="1:6" x14ac:dyDescent="0.3">
@@ -12122,7 +12152,7 @@
         <v>3.16759096364152</v>
       </c>
       <c r="F426" t="s">
-        <v>956</v>
+        <v>952</v>
       </c>
     </row>
     <row r="427" spans="1:6" x14ac:dyDescent="0.3">
@@ -12142,7 +12172,7 @@
         <v>3.1372318358276901</v>
       </c>
       <c r="F427" t="s">
-        <v>957</v>
+        <v>953</v>
       </c>
     </row>
     <row r="428" spans="1:6" x14ac:dyDescent="0.3">
@@ -12162,7 +12192,7 @@
         <v>3.0979373157222398</v>
       </c>
       <c r="F428" t="s">
-        <v>919</v>
+        <v>915</v>
       </c>
     </row>
     <row r="429" spans="1:6" x14ac:dyDescent="0.3">
@@ -12182,7 +12212,7 @@
         <v>3.0841946160253899</v>
       </c>
       <c r="F429" t="s">
-        <v>812</v>
+        <v>808</v>
       </c>
     </row>
     <row r="430" spans="1:6" x14ac:dyDescent="0.3">
@@ -12202,7 +12232,7 @@
         <v>3.0768042786346999</v>
       </c>
       <c r="F430" t="s">
-        <v>958</v>
+        <v>954</v>
       </c>
     </row>
     <row r="431" spans="1:6" x14ac:dyDescent="0.3">
@@ -12222,7 +12252,7 @@
         <v>3.0750751288370801</v>
       </c>
       <c r="F431" t="s">
-        <v>959</v>
+        <v>955</v>
       </c>
     </row>
     <row r="432" spans="1:6" x14ac:dyDescent="0.3">
@@ -12242,7 +12272,7 @@
         <v>3.0747739530842</v>
       </c>
       <c r="F432" t="s">
-        <v>960</v>
+        <v>956</v>
       </c>
     </row>
     <row r="433" spans="1:6" x14ac:dyDescent="0.3">
@@ -12262,7 +12292,7 @@
         <v>3.0726933146901199</v>
       </c>
       <c r="F433" t="s">
-        <v>961</v>
+        <v>957</v>
       </c>
     </row>
     <row r="434" spans="1:6" x14ac:dyDescent="0.3">
@@ -12282,7 +12312,7 @@
         <v>3.0725642445244299</v>
       </c>
       <c r="F434" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
     </row>
     <row r="435" spans="1:6" x14ac:dyDescent="0.3">
@@ -12302,7 +12332,7 @@
         <v>3.0658871263704</v>
       </c>
       <c r="F435" t="s">
-        <v>962</v>
+        <v>958</v>
       </c>
     </row>
     <row r="436" spans="1:6" x14ac:dyDescent="0.3">
@@ -12322,7 +12352,7 @@
         <v>3.0296398518988901</v>
       </c>
       <c r="F436" t="s">
-        <v>963</v>
+        <v>959</v>
       </c>
     </row>
     <row r="437" spans="1:6" x14ac:dyDescent="0.3">
@@ -12342,7 +12372,7 @@
         <v>2.9835789931267298</v>
       </c>
       <c r="F437" t="s">
-        <v>964</v>
+        <v>960</v>
       </c>
     </row>
     <row r="438" spans="1:6" x14ac:dyDescent="0.3">
@@ -12362,7 +12392,7 @@
         <v>2.97778133870318</v>
       </c>
       <c r="F438" t="s">
-        <v>965</v>
+        <v>961</v>
       </c>
     </row>
     <row r="439" spans="1:6" x14ac:dyDescent="0.3">
@@ -12382,7 +12412,7 @@
         <v>2.9760870974935201</v>
       </c>
       <c r="F439" t="s">
-        <v>966</v>
+        <v>962</v>
       </c>
     </row>
     <row r="440" spans="1:6" x14ac:dyDescent="0.3">
@@ -12402,7 +12432,7 @@
         <v>2.9490051971460201</v>
       </c>
       <c r="F440" t="s">
-        <v>967</v>
+        <v>963</v>
       </c>
     </row>
     <row r="441" spans="1:6" x14ac:dyDescent="0.3">
@@ -12422,7 +12452,7 @@
         <v>2.9424877590351799</v>
       </c>
       <c r="F441" t="s">
-        <v>968</v>
+        <v>964</v>
       </c>
     </row>
     <row r="442" spans="1:6" x14ac:dyDescent="0.3">
@@ -12442,7 +12472,7 @@
         <v>2.9411816076782502</v>
       </c>
       <c r="F442" t="s">
-        <v>969</v>
+        <v>965</v>
       </c>
     </row>
     <row r="443" spans="1:6" x14ac:dyDescent="0.3">
@@ -12462,7 +12492,7 @@
         <v>2.9406724963709601</v>
       </c>
       <c r="F443" t="s">
-        <v>970</v>
+        <v>966</v>
       </c>
     </row>
     <row r="444" spans="1:6" x14ac:dyDescent="0.3">
@@ -12482,7 +12512,7 @@
         <v>2.93165502722441</v>
       </c>
       <c r="F444" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
     </row>
     <row r="445" spans="1:6" x14ac:dyDescent="0.3">
@@ -12502,7 +12532,7 @@
         <v>2.9185610946143101</v>
       </c>
       <c r="F445" t="s">
-        <v>972</v>
+        <v>968</v>
       </c>
     </row>
     <row r="446" spans="1:6" x14ac:dyDescent="0.3">
@@ -12522,7 +12552,7 @@
         <v>2.8965365394596301</v>
       </c>
       <c r="F446" t="s">
-        <v>973</v>
+        <v>969</v>
       </c>
     </row>
     <row r="447" spans="1:6" x14ac:dyDescent="0.3">
@@ -12542,7 +12572,7 @@
         <v>2.8864154111035498</v>
       </c>
       <c r="F447" t="s">
-        <v>944</v>
+        <v>940</v>
       </c>
     </row>
     <row r="448" spans="1:6" x14ac:dyDescent="0.3">
@@ -12562,7 +12592,7 @@
         <v>2.8657137118217402</v>
       </c>
       <c r="F448" t="s">
-        <v>974</v>
+        <v>970</v>
       </c>
     </row>
     <row r="449" spans="1:6" x14ac:dyDescent="0.3">
@@ -12582,7 +12612,7 @@
         <v>2.8398715690385101</v>
       </c>
       <c r="F449" t="s">
-        <v>975</v>
+        <v>971</v>
       </c>
     </row>
     <row r="450" spans="1:6" x14ac:dyDescent="0.3">
@@ -12602,7 +12632,7 @@
         <v>2.8266465076320002</v>
       </c>
       <c r="F450" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
     </row>
     <row r="451" spans="1:6" x14ac:dyDescent="0.3">
@@ -12622,7 +12652,7 @@
         <v>2.8215480990553101</v>
       </c>
       <c r="F451" t="s">
-        <v>976</v>
+        <v>972</v>
       </c>
     </row>
     <row r="452" spans="1:6" x14ac:dyDescent="0.3">
@@ -12642,7 +12672,7 @@
         <v>2.7642302138219601</v>
       </c>
       <c r="F452" t="s">
-        <v>977</v>
+        <v>973</v>
       </c>
     </row>
     <row r="453" spans="1:6" x14ac:dyDescent="0.3">
@@ -12662,7 +12692,7 @@
         <v>2.7507471424179601</v>
       </c>
       <c r="F453" t="s">
-        <v>978</v>
+        <v>974</v>
       </c>
     </row>
     <row r="454" spans="1:6" x14ac:dyDescent="0.3">
@@ -12682,7 +12712,7 @@
         <v>2.73332856193645</v>
       </c>
       <c r="F454" t="s">
-        <v>979</v>
+        <v>975</v>
       </c>
     </row>
     <row r="455" spans="1:6" x14ac:dyDescent="0.3">
@@ -12702,7 +12732,7 @@
         <v>2.7294578743669802</v>
       </c>
       <c r="F455" t="s">
-        <v>815</v>
+        <v>811</v>
       </c>
     </row>
     <row r="456" spans="1:6" x14ac:dyDescent="0.3">
@@ -12722,7 +12752,7 @@
         <v>2.7250329854952802</v>
       </c>
       <c r="F456" t="s">
-        <v>980</v>
+        <v>976</v>
       </c>
     </row>
     <row r="457" spans="1:6" x14ac:dyDescent="0.3">
@@ -12742,7 +12772,7 @@
         <v>2.6590727280667998</v>
       </c>
       <c r="F457" t="s">
-        <v>981</v>
+        <v>977</v>
       </c>
     </row>
     <row r="458" spans="1:6" x14ac:dyDescent="0.3">
@@ -12762,7 +12792,7 @@
         <v>2.6497191028735601</v>
       </c>
       <c r="F458" t="s">
-        <v>832</v>
+        <v>828</v>
       </c>
     </row>
     <row r="459" spans="1:6" x14ac:dyDescent="0.3">
@@ -12782,7 +12812,7 @@
         <v>2.64149268098401</v>
       </c>
       <c r="F459" t="s">
-        <v>982</v>
+        <v>978</v>
       </c>
     </row>
     <row r="460" spans="1:6" x14ac:dyDescent="0.3">
@@ -12802,7 +12832,7 @@
         <v>2.6369812049122299</v>
       </c>
       <c r="F460" t="s">
-        <v>983</v>
+        <v>979</v>
       </c>
     </row>
     <row r="461" spans="1:6" x14ac:dyDescent="0.3">
@@ -12822,7 +12852,7 @@
         <v>2.6369812049122299</v>
       </c>
       <c r="F461" t="s">
-        <v>984</v>
+        <v>980</v>
       </c>
     </row>
     <row r="462" spans="1:6" x14ac:dyDescent="0.3">
@@ -12842,7 +12872,7 @@
         <v>2.6179478736619899</v>
       </c>
       <c r="F462" t="s">
-        <v>985</v>
+        <v>981</v>
       </c>
     </row>
     <row r="463" spans="1:6" x14ac:dyDescent="0.3">
@@ -12862,7 +12892,7 @@
         <v>2.6075105599689401</v>
       </c>
       <c r="F463" t="s">
-        <v>986</v>
+        <v>982</v>
       </c>
     </row>
     <row r="464" spans="1:6" x14ac:dyDescent="0.3">
@@ -12882,7 +12912,7 @@
         <v>2.6047618707897402</v>
       </c>
       <c r="F464" t="s">
-        <v>987</v>
+        <v>983</v>
       </c>
     </row>
     <row r="465" spans="1:6" x14ac:dyDescent="0.3">
@@ -12902,7 +12932,7 @@
         <v>2.6028693780267198</v>
       </c>
       <c r="F465" t="s">
-        <v>988</v>
+        <v>984</v>
       </c>
     </row>
     <row r="466" spans="1:6" x14ac:dyDescent="0.3">
@@ -12922,7 +12952,7 @@
         <v>2.5943347504148502</v>
       </c>
       <c r="F466" t="s">
-        <v>715</v>
+        <v>711</v>
       </c>
     </row>
     <row r="467" spans="1:6" x14ac:dyDescent="0.3">
@@ -12942,7 +12972,7 @@
         <v>2.5664758908647198</v>
       </c>
       <c r="F467" t="s">
-        <v>989</v>
+        <v>985</v>
       </c>
     </row>
     <row r="468" spans="1:6" x14ac:dyDescent="0.3">
@@ -12962,7 +12992,7 @@
         <v>2.5440695332448899</v>
       </c>
       <c r="F468" t="s">
-        <v>990</v>
+        <v>986</v>
       </c>
     </row>
     <row r="469" spans="1:6" x14ac:dyDescent="0.3">
@@ -12982,7 +13012,7 @@
         <v>2.5392404975792702</v>
       </c>
       <c r="F469" t="s">
-        <v>991</v>
+        <v>987</v>
       </c>
     </row>
     <row r="470" spans="1:6" x14ac:dyDescent="0.3">
@@ -13002,7 +13032,7 @@
         <v>2.53724254194965</v>
       </c>
       <c r="F470" t="s">
-        <v>992</v>
+        <v>988</v>
       </c>
     </row>
     <row r="471" spans="1:6" x14ac:dyDescent="0.3">
@@ -13022,7 +13052,7 @@
         <v>2.5340164931152298</v>
       </c>
       <c r="F471" t="s">
-        <v>993</v>
+        <v>989</v>
       </c>
     </row>
     <row r="472" spans="1:6" x14ac:dyDescent="0.3">
@@ -13042,7 +13072,7 @@
         <v>2.4986424943073899</v>
       </c>
       <c r="F472" t="s">
-        <v>777</v>
+        <v>773</v>
       </c>
     </row>
     <row r="473" spans="1:6" x14ac:dyDescent="0.3">
@@ -13062,7 +13092,7 @@
         <v>2.4786571634568002</v>
       </c>
       <c r="F473" t="s">
-        <v>994</v>
+        <v>990</v>
       </c>
     </row>
     <row r="474" spans="1:6" x14ac:dyDescent="0.3">
@@ -13082,7 +13112,7 @@
         <v>2.47145346439099</v>
       </c>
       <c r="F474" t="s">
-        <v>995</v>
+        <v>991</v>
       </c>
     </row>
     <row r="475" spans="1:6" x14ac:dyDescent="0.3">
@@ -13102,7 +13132,7 @@
         <v>2.4650037062673</v>
       </c>
       <c r="F475" t="s">
-        <v>996</v>
+        <v>992</v>
       </c>
     </row>
     <row r="476" spans="1:6" x14ac:dyDescent="0.3">
@@ -13122,7 +13152,7 @@
         <v>2.4600687451982801</v>
       </c>
       <c r="F476" t="s">
-        <v>802</v>
+        <v>798</v>
       </c>
     </row>
     <row r="477" spans="1:6" x14ac:dyDescent="0.3">
@@ -13142,7 +13172,7 @@
         <v>2.45521117877604</v>
       </c>
       <c r="F477" t="s">
-        <v>997</v>
+        <v>993</v>
       </c>
     </row>
     <row r="478" spans="1:6" x14ac:dyDescent="0.3">
@@ -13162,7 +13192,7 @@
         <v>2.4423470353691998</v>
       </c>
       <c r="F478" t="s">
-        <v>998</v>
+        <v>994</v>
       </c>
     </row>
     <row r="479" spans="1:6" x14ac:dyDescent="0.3">
@@ -13182,7 +13212,7 @@
         <v>2.3716536019915999</v>
       </c>
       <c r="F479" t="s">
-        <v>999</v>
+        <v>995</v>
       </c>
     </row>
     <row r="480" spans="1:6" x14ac:dyDescent="0.3">
@@ -13202,7 +13232,7 @@
         <v>2.35226053061103</v>
       </c>
       <c r="F480" t="s">
-        <v>1000</v>
+        <v>996</v>
       </c>
     </row>
     <row r="481" spans="1:6" x14ac:dyDescent="0.3">
@@ -13222,7 +13252,7 @@
         <v>2.3362346334044801</v>
       </c>
       <c r="F481" t="s">
-        <v>1001</v>
+        <v>997</v>
       </c>
     </row>
     <row r="482" spans="1:6" x14ac:dyDescent="0.3">
@@ -13242,7 +13272,7 @@
         <v>2.32148813955023</v>
       </c>
       <c r="F482" t="s">
-        <v>900</v>
+        <v>896</v>
       </c>
     </row>
     <row r="483" spans="1:6" x14ac:dyDescent="0.3">
@@ -13262,7 +13292,7 @@
         <v>2.29378588755241</v>
       </c>
       <c r="F483" t="s">
-        <v>1002</v>
+        <v>998</v>
       </c>
     </row>
     <row r="484" spans="1:6" x14ac:dyDescent="0.3">
@@ -13282,7 +13312,7 @@
         <v>2.28267129884749</v>
       </c>
       <c r="F484" t="s">
-        <v>1003</v>
+        <v>999</v>
       </c>
     </row>
     <row r="485" spans="1:6" x14ac:dyDescent="0.3">
@@ -13302,7 +13332,7 @@
         <v>2.2602789203776799</v>
       </c>
       <c r="F485" t="s">
-        <v>1004</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="486" spans="1:6" x14ac:dyDescent="0.3">
@@ -13322,7 +13352,7 @@
         <v>2.2403359160315102</v>
       </c>
       <c r="F486" t="s">
-        <v>1005</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="487" spans="1:6" x14ac:dyDescent="0.3">
@@ -13342,7 +13372,7 @@
         <v>2.2366610854987998</v>
       </c>
       <c r="F487" t="s">
-        <v>1006</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="488" spans="1:6" x14ac:dyDescent="0.3">
@@ -13362,7 +13392,7 @@
         <v>2.2352423859749</v>
       </c>
       <c r="F488" t="s">
-        <v>927</v>
+        <v>923</v>
       </c>
     </row>
     <row r="489" spans="1:6" x14ac:dyDescent="0.3">
@@ -13382,7 +13412,7 @@
         <v>2.2268761781284598</v>
       </c>
       <c r="F489" t="s">
-        <v>1007</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="490" spans="1:6" x14ac:dyDescent="0.3">
@@ -13402,7 +13432,7 @@
         <v>2.2174272846537399</v>
       </c>
       <c r="F490" t="s">
-        <v>1008</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="491" spans="1:6" x14ac:dyDescent="0.3">
@@ -13422,7 +13452,7 @@
         <v>2.19722457733622</v>
       </c>
       <c r="F491" t="s">
-        <v>1009</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="492" spans="1:6" x14ac:dyDescent="0.3">
@@ -13442,7 +13472,7 @@
         <v>2.1951594793232601</v>
       </c>
       <c r="F492" t="s">
-        <v>1010</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="493" spans="1:6" x14ac:dyDescent="0.3">
@@ -13462,7 +13492,7 @@
         <v>2.1841963937076199</v>
       </c>
       <c r="F493" t="s">
-        <v>1011</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="494" spans="1:6" x14ac:dyDescent="0.3">
@@ -13482,7 +13512,7 @@
         <v>2.1725458227851702</v>
       </c>
       <c r="F494" t="s">
-        <v>1012</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="495" spans="1:6" x14ac:dyDescent="0.3">
@@ -13502,7 +13532,7 @@
         <v>2.1661509407115598</v>
       </c>
       <c r="F495" t="s">
-        <v>1013</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="496" spans="1:6" x14ac:dyDescent="0.3">
@@ -13522,7 +13552,7 @@
         <v>2.16080106690712</v>
       </c>
       <c r="F496" t="s">
-        <v>1014</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="497" spans="1:6" x14ac:dyDescent="0.3">
@@ -13542,7 +13572,7 @@
         <v>2.1594842493533699</v>
       </c>
       <c r="F497" t="s">
-        <v>1015</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="498" spans="1:6" x14ac:dyDescent="0.3">
@@ -13562,7 +13592,7 @@
         <v>2.1525732280466499</v>
       </c>
       <c r="F498" t="s">
-        <v>900</v>
+        <v>896</v>
       </c>
     </row>
     <row r="499" spans="1:6" x14ac:dyDescent="0.3">
@@ -13582,7 +13612,7 @@
         <v>2.1495529386680099</v>
       </c>
       <c r="F499" t="s">
-        <v>1016</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="500" spans="1:6" x14ac:dyDescent="0.3">
@@ -13602,7 +13632,7 @@
         <v>2.1165356660860799</v>
       </c>
       <c r="F500" t="s">
-        <v>1017</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="501" spans="1:6" x14ac:dyDescent="0.3">
@@ -13622,7 +13652,7 @@
         <v>2.1131281048492201</v>
       </c>
       <c r="F501" t="s">
-        <v>683</v>
+        <v>679</v>
       </c>
     </row>
     <row r="502" spans="1:6" x14ac:dyDescent="0.3">
@@ -13642,7 +13672,7 @@
         <v>2.1110043300287602</v>
       </c>
       <c r="F502" t="s">
-        <v>900</v>
+        <v>896</v>
       </c>
     </row>
     <row r="503" spans="1:6" x14ac:dyDescent="0.3">
@@ -13662,7 +13692,7 @@
         <v>2.1080096147014298</v>
       </c>
       <c r="F503" t="s">
-        <v>1018</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="504" spans="1:6" x14ac:dyDescent="0.3">
@@ -13682,7 +13712,7 @@
         <v>2.09567217955128</v>
       </c>
       <c r="F504" t="s">
-        <v>727</v>
+        <v>723</v>
       </c>
     </row>
     <row r="505" spans="1:6" x14ac:dyDescent="0.3">
@@ -13702,7 +13732,7 @@
         <v>2.0828814565843699</v>
       </c>
       <c r="F505" t="s">
-        <v>1019</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="506" spans="1:6" x14ac:dyDescent="0.3">
@@ -13722,7 +13752,7 @@
         <v>2.06289457233569</v>
       </c>
       <c r="F506" t="s">
-        <v>1020</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="507" spans="1:6" x14ac:dyDescent="0.3">
@@ -13742,7 +13772,7 @@
         <v>2.0622491411394601</v>
       </c>
       <c r="F507" t="s">
-        <v>1021</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="508" spans="1:6" x14ac:dyDescent="0.3">
@@ -13762,7 +13792,7 @@
         <v>2.0595079135238299</v>
       </c>
       <c r="F508" t="s">
-        <v>1022</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="509" spans="1:6" x14ac:dyDescent="0.3">
@@ -13782,7 +13812,7 @@
         <v>2.05931480767154</v>
       </c>
       <c r="F509" t="s">
-        <v>802</v>
+        <v>798</v>
       </c>
     </row>
     <row r="510" spans="1:6" x14ac:dyDescent="0.3">
@@ -13802,7 +13832,7 @@
         <v>2.0221382764028899</v>
       </c>
       <c r="F510" t="s">
-        <v>1023</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="511" spans="1:6" x14ac:dyDescent="0.3">
@@ -13822,7 +13852,7 @@
         <v>1.9988118072797301</v>
       </c>
       <c r="F511" t="s">
-        <v>1024</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="512" spans="1:6" x14ac:dyDescent="0.3">
@@ -13842,7 +13872,7 @@
         <v>1.98309220508432</v>
       </c>
       <c r="F512" t="s">
-        <v>1025</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="513" spans="1:6" x14ac:dyDescent="0.3">
@@ -13862,7 +13892,7 @@
         <v>1.98100146886658</v>
       </c>
       <c r="F513" t="s">
-        <v>1026</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="514" spans="1:6" x14ac:dyDescent="0.3">
@@ -13882,7 +13912,7 @@
         <v>1.9704151063441899</v>
       </c>
       <c r="F514" t="s">
-        <v>1027</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="515" spans="1:6" x14ac:dyDescent="0.3">
@@ -13902,7 +13932,7 @@
         <v>1.9690522838176401</v>
       </c>
       <c r="F515" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
     </row>
     <row r="516" spans="1:6" x14ac:dyDescent="0.3">
@@ -13922,7 +13952,7 @@
         <v>1.95772638187044</v>
       </c>
       <c r="F516" t="s">
-        <v>1028</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="517" spans="1:6" x14ac:dyDescent="0.3">
@@ -13942,7 +13972,7 @@
         <v>1.9299639013556</v>
       </c>
       <c r="F517" t="s">
-        <v>1029</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="518" spans="1:6" x14ac:dyDescent="0.3">
@@ -13962,7 +13992,7 @@
         <v>1.8840557305372401</v>
       </c>
       <c r="F518" t="s">
-        <v>1030</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="519" spans="1:6" x14ac:dyDescent="0.3">
@@ -13982,7 +14012,7 @@
         <v>1.8817856208857699</v>
       </c>
       <c r="F519" t="s">
-        <v>1031</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="520" spans="1:6" x14ac:dyDescent="0.3">
@@ -14002,7 +14032,7 @@
         <v>1.87167233248666</v>
       </c>
       <c r="F520" t="s">
-        <v>1032</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="521" spans="1:6" x14ac:dyDescent="0.3">
@@ -14022,7 +14052,7 @@
         <v>1.86685402823428</v>
       </c>
       <c r="F521" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
     </row>
     <row r="522" spans="1:6" x14ac:dyDescent="0.3">
@@ -14042,7 +14072,7 @@
         <v>1.8607689899000299</v>
       </c>
       <c r="F522" t="s">
-        <v>1033</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="523" spans="1:6" x14ac:dyDescent="0.3">
@@ -14062,7 +14092,7 @@
         <v>1.8570013809790999</v>
       </c>
       <c r="F523" t="s">
-        <v>1034</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="524" spans="1:6" x14ac:dyDescent="0.3">
@@ -14082,7 +14112,7 @@
         <v>1.8403084533984</v>
       </c>
       <c r="F524" t="s">
-        <v>889</v>
+        <v>885</v>
       </c>
     </row>
     <row r="525" spans="1:6" x14ac:dyDescent="0.3">
@@ -14102,7 +14132,7 @@
         <v>1.8327700675047101</v>
       </c>
       <c r="F525" t="s">
-        <v>1035</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="526" spans="1:6" x14ac:dyDescent="0.3">
@@ -14122,7 +14152,7 @@
         <v>1.8280072596204</v>
       </c>
       <c r="F526" t="s">
-        <v>987</v>
+        <v>983</v>
       </c>
     </row>
     <row r="527" spans="1:6" x14ac:dyDescent="0.3">
@@ -14142,7 +14172,7 @@
         <v>1.82427116661468</v>
       </c>
       <c r="F527" t="s">
-        <v>1036</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="528" spans="1:6" x14ac:dyDescent="0.3">
@@ -14162,7 +14192,7 @@
         <v>1.8191584434161701</v>
       </c>
       <c r="F528" t="s">
-        <v>1037</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="529" spans="1:6" x14ac:dyDescent="0.3">
@@ -14182,7 +14212,7 @@
         <v>1.8108299311580001</v>
       </c>
       <c r="F529" t="s">
-        <v>1038</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="530" spans="1:6" x14ac:dyDescent="0.3">
@@ -14202,7 +14232,7 @@
         <v>1.8050046959780801</v>
       </c>
       <c r="F530" t="s">
-        <v>745</v>
+        <v>741</v>
       </c>
     </row>
     <row r="531" spans="1:6" x14ac:dyDescent="0.3">
@@ -14222,7 +14252,7 @@
         <v>1.79732516827058</v>
       </c>
       <c r="F531" t="s">
-        <v>1039</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="532" spans="1:6" x14ac:dyDescent="0.3">
@@ -14242,7 +14272,7 @@
         <v>1.7854503000347901</v>
       </c>
       <c r="F532" t="s">
-        <v>812</v>
+        <v>808</v>
       </c>
     </row>
     <row r="533" spans="1:6" x14ac:dyDescent="0.3">
@@ -14262,7 +14292,7 @@
         <v>1.7640648896647</v>
       </c>
       <c r="F533" t="s">
-        <v>772</v>
+        <v>768</v>
       </c>
     </row>
     <row r="534" spans="1:6" x14ac:dyDescent="0.3">
@@ -14282,7 +14312,7 @@
         <v>1.7635885922613601</v>
       </c>
       <c r="F534" t="s">
-        <v>1040</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="535" spans="1:6" x14ac:dyDescent="0.3">
@@ -14302,7 +14332,7 @@
         <v>1.7546199222786001</v>
       </c>
       <c r="F535" t="s">
-        <v>1041</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="536" spans="1:6" x14ac:dyDescent="0.3">
@@ -14322,7 +14352,7 @@
         <v>1.7325745326094799</v>
       </c>
       <c r="F536" t="s">
-        <v>997</v>
+        <v>993</v>
       </c>
     </row>
     <row r="537" spans="1:6" x14ac:dyDescent="0.3">
@@ -14342,7 +14372,7 @@
         <v>1.7256437599622401</v>
       </c>
       <c r="F537" t="s">
-        <v>1042</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="538" spans="1:6" x14ac:dyDescent="0.3">
@@ -14362,7 +14392,7 @@
         <v>1.72272516537327</v>
       </c>
       <c r="F538" t="s">
-        <v>1043</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="539" spans="1:6" x14ac:dyDescent="0.3">
@@ -14382,7 +14412,7 @@
         <v>1.7012872055247299</v>
       </c>
       <c r="F539" t="s">
-        <v>1044</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="540" spans="1:6" x14ac:dyDescent="0.3">
@@ -14402,7 +14432,7 @@
         <v>1.67105159966442</v>
       </c>
       <c r="F540" t="s">
-        <v>920</v>
+        <v>916</v>
       </c>
     </row>
     <row r="541" spans="1:6" x14ac:dyDescent="0.3">
@@ -14422,7 +14452,7 @@
         <v>1.6562217414231399</v>
       </c>
       <c r="F541" t="s">
-        <v>828</v>
+        <v>824</v>
       </c>
     </row>
     <row r="542" spans="1:6" x14ac:dyDescent="0.3">
@@ -14442,7 +14472,7 @@
         <v>1.6453632515012899</v>
       </c>
       <c r="F542" t="s">
-        <v>1045</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="543" spans="1:6" x14ac:dyDescent="0.3">
@@ -14462,7 +14492,7 @@
         <v>1.64222773525709</v>
       </c>
       <c r="F543" t="s">
-        <v>673</v>
+        <v>669</v>
       </c>
     </row>
     <row r="544" spans="1:6" x14ac:dyDescent="0.3">
@@ -14482,7 +14512,7 @@
         <v>1.6368368866222101</v>
       </c>
       <c r="F544" t="s">
-        <v>1046</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="545" spans="1:6" x14ac:dyDescent="0.3">
@@ -14502,7 +14532,7 @@
         <v>1.6282121773954801</v>
       </c>
       <c r="F545" t="s">
-        <v>1047</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="546" spans="1:6" x14ac:dyDescent="0.3">
@@ -14522,7 +14552,7 @@
         <v>1.6262450307504801</v>
       </c>
       <c r="F546" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
     </row>
     <row r="547" spans="1:6" x14ac:dyDescent="0.3">
@@ -14542,7 +14572,7 @@
         <v>1.62270216262587</v>
       </c>
       <c r="F547" t="s">
-        <v>1048</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="548" spans="1:6" x14ac:dyDescent="0.3">
@@ -14562,7 +14592,7 @@
         <v>1.60102035431457</v>
       </c>
       <c r="F548" t="s">
-        <v>1049</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="549" spans="1:6" x14ac:dyDescent="0.3">
@@ -14582,7 +14612,7 @@
         <v>1.5649708196018</v>
       </c>
       <c r="F549" t="s">
-        <v>880</v>
+        <v>876</v>
       </c>
     </row>
     <row r="550" spans="1:6" x14ac:dyDescent="0.3">
@@ -14602,7 +14632,7 @@
         <v>1.5553004875852201</v>
       </c>
       <c r="F550" t="s">
-        <v>819</v>
+        <v>815</v>
       </c>
     </row>
     <row r="551" spans="1:6" x14ac:dyDescent="0.3">
@@ -14622,7 +14652,7 @@
         <v>1.5355127439498599</v>
       </c>
       <c r="F551" t="s">
-        <v>1011</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="552" spans="1:6" x14ac:dyDescent="0.3">
@@ -14642,7 +14672,7 @@
         <v>1.51468290923918</v>
       </c>
       <c r="F552" t="s">
-        <v>829</v>
+        <v>825</v>
       </c>
     </row>
     <row r="553" spans="1:6" x14ac:dyDescent="0.3">
@@ -14662,7 +14692,7 @@
         <v>1.49224293912927</v>
       </c>
       <c r="F553" t="s">
-        <v>1050</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="554" spans="1:6" x14ac:dyDescent="0.3">
@@ -14682,7 +14712,7 @@
         <v>1.47810191037301</v>
       </c>
       <c r="F554" t="s">
-        <v>1051</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="555" spans="1:6" x14ac:dyDescent="0.3">
@@ -14702,7 +14732,7 @@
         <v>1.47810191037301</v>
       </c>
       <c r="F555" t="s">
-        <v>1052</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="556" spans="1:6" x14ac:dyDescent="0.3">
@@ -14722,7 +14752,7 @@
         <v>1.4643753222103899</v>
       </c>
       <c r="F556" t="s">
-        <v>1053</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="557" spans="1:6" x14ac:dyDescent="0.3">
@@ -14742,7 +14772,7 @@
         <v>1.44691898293633</v>
       </c>
       <c r="F557" t="s">
-        <v>676</v>
+        <v>672</v>
       </c>
     </row>
     <row r="558" spans="1:6" x14ac:dyDescent="0.3">
@@ -14762,7 +14792,7 @@
         <v>1.4436456575913601</v>
       </c>
       <c r="F558" t="s">
-        <v>1054</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="559" spans="1:6" x14ac:dyDescent="0.3">
@@ -14782,7 +14812,7 @@
         <v>1.44121011871601</v>
       </c>
       <c r="F559" t="s">
-        <v>1055</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="560" spans="1:6" x14ac:dyDescent="0.3">
@@ -14802,7 +14832,7 @@
         <v>1.42172813383901</v>
       </c>
       <c r="F560" t="s">
-        <v>1056</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="561" spans="1:6" x14ac:dyDescent="0.3">
@@ -14822,7 +14852,7 @@
         <v>1.41259706198904</v>
       </c>
       <c r="F561" t="s">
-        <v>1057</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="562" spans="1:6" x14ac:dyDescent="0.3">
@@ -14842,7 +14872,7 @@
         <v>1.4035876301475001</v>
       </c>
       <c r="F562" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
     </row>
     <row r="563" spans="1:6" x14ac:dyDescent="0.3">
@@ -14862,7 +14892,7 @@
         <v>1.3913188371246099</v>
       </c>
       <c r="F563" t="s">
-        <v>868</v>
+        <v>864</v>
       </c>
     </row>
     <row r="564" spans="1:6" x14ac:dyDescent="0.3">
@@ -14882,7 +14912,7 @@
         <v>1.3903185114196199</v>
       </c>
       <c r="F564" t="s">
-        <v>1058</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="565" spans="1:6" x14ac:dyDescent="0.3">
@@ -14902,7 +14932,7 @@
         <v>1.3862943611198899</v>
       </c>
       <c r="F565" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
     </row>
     <row r="566" spans="1:6" x14ac:dyDescent="0.3">
@@ -14922,7 +14952,7 @@
         <v>1.37912587164128</v>
       </c>
       <c r="F566" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
     </row>
     <row r="567" spans="1:6" x14ac:dyDescent="0.3">
@@ -14942,7 +14972,7 @@
         <v>1.3511623944821201</v>
       </c>
       <c r="F567" t="s">
-        <v>1059</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="568" spans="1:6" x14ac:dyDescent="0.3">
@@ -14962,7 +14992,7 @@
         <v>1.3245887030666199</v>
       </c>
       <c r="F568" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
     </row>
     <row r="569" spans="1:6" x14ac:dyDescent="0.3">
@@ -14982,7 +15012,7 @@
         <v>1.3114923071603499</v>
       </c>
       <c r="F569" t="s">
-        <v>1060</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="570" spans="1:6" x14ac:dyDescent="0.3">
@@ -15002,7 +15032,7 @@
         <v>1.30474449415578</v>
       </c>
       <c r="F570" t="s">
-        <v>1061</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="571" spans="1:6" x14ac:dyDescent="0.3">
@@ -15022,7 +15052,7 @@
         <v>1.2970076702931299</v>
       </c>
       <c r="F571" t="s">
-        <v>1062</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="572" spans="1:6" x14ac:dyDescent="0.3">
@@ -15042,7 +15072,7 @@
         <v>1.2910426367455601</v>
       </c>
       <c r="F572" t="s">
-        <v>802</v>
+        <v>798</v>
       </c>
     </row>
     <row r="573" spans="1:6" x14ac:dyDescent="0.3">
@@ -15062,7 +15092,7 @@
         <v>1.2783921140191801</v>
       </c>
       <c r="F573" t="s">
-        <v>1063</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="574" spans="1:6" x14ac:dyDescent="0.3">
@@ -15082,7 +15112,7 @@
         <v>1.2546659186414499</v>
       </c>
       <c r="F574" t="s">
-        <v>773</v>
+        <v>769</v>
       </c>
     </row>
     <row r="575" spans="1:6" x14ac:dyDescent="0.3">
@@ -15102,7 +15132,7 @@
         <v>1.2431828745106399</v>
       </c>
       <c r="F575" t="s">
-        <v>1012</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="576" spans="1:6" x14ac:dyDescent="0.3">
@@ -15122,7 +15152,7 @@
         <v>1.23235597298221</v>
       </c>
       <c r="F576" t="s">
-        <v>703</v>
+        <v>699</v>
       </c>
     </row>
     <row r="577" spans="1:6" x14ac:dyDescent="0.3">
@@ -15142,7 +15172,7 @@
         <v>1.19924466312999</v>
       </c>
       <c r="F577" t="s">
-        <v>1064</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="578" spans="1:6" x14ac:dyDescent="0.3">
@@ -15162,7 +15192,7 @@
         <v>1.1856236656577399</v>
       </c>
       <c r="F578" t="s">
-        <v>773</v>
+        <v>769</v>
       </c>
     </row>
     <row r="579" spans="1:6" x14ac:dyDescent="0.3">
@@ -15182,7 +15212,7 @@
         <v>1.1741198411762499</v>
       </c>
       <c r="F579" t="s">
-        <v>1065</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="580" spans="1:6" x14ac:dyDescent="0.3">
@@ -15202,7 +15232,7 @@
         <v>1.16587680272047</v>
       </c>
       <c r="F580" t="s">
-        <v>824</v>
+        <v>820</v>
       </c>
     </row>
     <row r="581" spans="1:6" x14ac:dyDescent="0.3">
@@ -15222,7 +15252,7 @@
         <v>1.1583840319680301</v>
       </c>
       <c r="F581" t="s">
-        <v>1066</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="582" spans="1:6" x14ac:dyDescent="0.3">
@@ -15242,7 +15272,7 @@
         <v>1.1564318595569401</v>
       </c>
       <c r="F582" t="s">
-        <v>813</v>
+        <v>809</v>
       </c>
     </row>
     <row r="583" spans="1:6" x14ac:dyDescent="0.3">
@@ -15262,7 +15292,7 @@
         <v>1.15351458305581</v>
       </c>
       <c r="F583" t="s">
-        <v>1067</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="584" spans="1:6" x14ac:dyDescent="0.3">
@@ -15282,7 +15312,7 @@
         <v>1.1508113306526899</v>
       </c>
       <c r="F584" t="s">
-        <v>1068</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="585" spans="1:6" x14ac:dyDescent="0.3">
@@ -15302,7 +15332,7 @@
         <v>1.1494335717792601</v>
       </c>
       <c r="F585" t="s">
-        <v>1069</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="586" spans="1:6" x14ac:dyDescent="0.3">
@@ -15322,7 +15352,7 @@
         <v>1.1414759930998899</v>
       </c>
       <c r="F586" t="s">
-        <v>885</v>
+        <v>881</v>
       </c>
     </row>
     <row r="587" spans="1:6" x14ac:dyDescent="0.3">
@@ -15342,7 +15372,7 @@
         <v>1.1394342831883599</v>
       </c>
       <c r="F587" t="s">
-        <v>1070</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="588" spans="1:6" x14ac:dyDescent="0.3">
@@ -15362,7 +15392,7 @@
         <v>1.13835306394489</v>
       </c>
       <c r="F588" t="s">
-        <v>1071</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="589" spans="1:6" x14ac:dyDescent="0.3">
@@ -15382,7 +15412,7 @@
         <v>1.12077995772408</v>
       </c>
       <c r="F589" t="s">
-        <v>1072</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="590" spans="1:6" x14ac:dyDescent="0.3">
@@ -15402,7 +15432,7 @@
         <v>1.1141970995929</v>
       </c>
       <c r="F590" t="s">
-        <v>720</v>
+        <v>716</v>
       </c>
     </row>
     <row r="591" spans="1:6" x14ac:dyDescent="0.3">
@@ -15422,7 +15452,7 @@
         <v>1.1058325366416</v>
       </c>
       <c r="F591" t="s">
-        <v>1073</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="592" spans="1:6" x14ac:dyDescent="0.3">
@@ -15442,7 +15472,7 @@
         <v>1.09317501918229</v>
       </c>
       <c r="F592" t="s">
-        <v>693</v>
+        <v>689</v>
       </c>
     </row>
     <row r="593" spans="1:6" x14ac:dyDescent="0.3">
@@ -15462,7 +15492,7 @@
         <v>1.09018908460552</v>
       </c>
       <c r="F593" t="s">
-        <v>1074</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="594" spans="1:6" x14ac:dyDescent="0.3">
@@ -15482,7 +15512,7 @@
         <v>1.05458272127202</v>
       </c>
       <c r="F594" t="s">
-        <v>1060</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="595" spans="1:6" x14ac:dyDescent="0.3">
@@ -15502,7 +15532,7 @@
         <v>1.0068047394149899</v>
       </c>
       <c r="F595" t="s">
-        <v>1075</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="596" spans="1:6" x14ac:dyDescent="0.3">
@@ -15522,7 +15552,7 @@
         <v>1.0018517822861399</v>
       </c>
       <c r="F596" t="s">
-        <v>1076</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="597" spans="1:6" x14ac:dyDescent="0.3">
@@ -15542,7 +15572,7 @@
         <v>0.990398704027877</v>
       </c>
       <c r="F597" t="s">
-        <v>900</v>
+        <v>896</v>
       </c>
     </row>
     <row r="598" spans="1:6" x14ac:dyDescent="0.3">
@@ -15562,7 +15592,7 @@
         <v>0.98910126628505701</v>
       </c>
       <c r="F598" t="s">
-        <v>671</v>
+        <v>667</v>
       </c>
     </row>
     <row r="599" spans="1:6" x14ac:dyDescent="0.3">
@@ -15582,7 +15612,7 @@
         <v>0.92943920471766095</v>
       </c>
       <c r="F599" t="s">
-        <v>1077</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="600" spans="1:6" x14ac:dyDescent="0.3">
@@ -15602,7 +15632,7 @@
         <v>0.92754788639878905</v>
       </c>
       <c r="F600" t="s">
-        <v>1078</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="601" spans="1:6" x14ac:dyDescent="0.3">
@@ -15622,7 +15652,7 @@
         <v>0.92714074789822098</v>
       </c>
       <c r="F601" t="s">
-        <v>1079</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="602" spans="1:6" x14ac:dyDescent="0.3">
@@ -15642,7 +15672,7 @@
         <v>0.92248456645253196</v>
       </c>
       <c r="F602" t="s">
-        <v>1080</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="603" spans="1:6" x14ac:dyDescent="0.3">
@@ -15662,7 +15692,7 @@
         <v>0.90825856017689099</v>
       </c>
       <c r="F603" t="s">
-        <v>1081</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="604" spans="1:6" x14ac:dyDescent="0.3">
@@ -15682,7 +15712,7 @@
         <v>0.86886805332254802</v>
       </c>
       <c r="F604" t="s">
-        <v>1082</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="605" spans="1:6" x14ac:dyDescent="0.3">
@@ -15702,7 +15732,7 @@
         <v>0.83840891296995801</v>
       </c>
       <c r="F605" t="s">
-        <v>802</v>
+        <v>798</v>
       </c>
     </row>
     <row r="606" spans="1:6" x14ac:dyDescent="0.3">
@@ -15722,7 +15752,7 @@
         <v>0.83103088792333202</v>
       </c>
       <c r="F606" t="s">
-        <v>1083</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="607" spans="1:6" x14ac:dyDescent="0.3">
@@ -15742,7 +15772,7 @@
         <v>0.80195167016312796</v>
       </c>
       <c r="F607" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
     </row>
     <row r="608" spans="1:6" x14ac:dyDescent="0.3">
@@ -15762,7 +15792,7 @@
         <v>0.77992959361039504</v>
       </c>
       <c r="F608" t="s">
-        <v>671</v>
+        <v>667</v>
       </c>
     </row>
     <row r="609" spans="1:6" x14ac:dyDescent="0.3">
@@ -15782,7 +15812,7 @@
         <v>0.74437476976661898</v>
       </c>
       <c r="F609" t="s">
-        <v>1084</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="610" spans="1:6" x14ac:dyDescent="0.3">
@@ -15802,7 +15832,7 @@
         <v>0.71824157816462497</v>
       </c>
       <c r="F610" t="s">
-        <v>1085</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="611" spans="1:6" x14ac:dyDescent="0.3">
@@ -15822,7 +15852,7 @@
         <v>0.71743987312899005</v>
       </c>
       <c r="F611" t="s">
-        <v>683</v>
+        <v>679</v>
       </c>
     </row>
     <row r="612" spans="1:6" x14ac:dyDescent="0.3">
@@ -15842,7 +15872,7 @@
         <v>0.69894429824427096</v>
       </c>
       <c r="F612" t="s">
-        <v>763</v>
+        <v>759</v>
       </c>
     </row>
     <row r="613" spans="1:6" x14ac:dyDescent="0.3">
@@ -15862,7 +15892,7 @@
         <v>0.69735181184197703</v>
       </c>
       <c r="F613" t="s">
-        <v>1086</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="614" spans="1:6" x14ac:dyDescent="0.3">
@@ -15882,7 +15912,7 @@
         <v>0.679252989949932</v>
       </c>
       <c r="F614" t="s">
-        <v>1087</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="615" spans="1:6" x14ac:dyDescent="0.3">
@@ -15902,7 +15932,7 @@
         <v>0.59508596738373098</v>
       </c>
       <c r="F615" t="s">
-        <v>1088</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="616" spans="1:6" x14ac:dyDescent="0.3">
@@ -15922,7 +15952,7 @@
         <v>0.59151453501613305</v>
       </c>
       <c r="F616" t="s">
-        <v>1089</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="617" spans="1:6" x14ac:dyDescent="0.3">
@@ -15942,7 +15972,7 @@
         <v>0.58778666490211895</v>
       </c>
       <c r="F617" t="s">
-        <v>802</v>
+        <v>798</v>
       </c>
     </row>
     <row r="618" spans="1:6" x14ac:dyDescent="0.3">
@@ -15962,7 +15992,7 @@
         <v>0.57804701560455996</v>
       </c>
       <c r="F618" t="s">
-        <v>1065</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="619" spans="1:6" x14ac:dyDescent="0.3">
@@ -15982,7 +16012,7 @@
         <v>0.57042096461854996</v>
       </c>
       <c r="F619" t="s">
-        <v>1090</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="620" spans="1:6" x14ac:dyDescent="0.3">
@@ -16002,7 +16032,7 @@
         <v>0.54300471345435397</v>
       </c>
       <c r="F620" t="s">
-        <v>1091</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="621" spans="1:6" x14ac:dyDescent="0.3">
@@ -16022,7 +16052,7 @@
         <v>0.52457317377158197</v>
       </c>
       <c r="F621" t="s">
-        <v>1092</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="622" spans="1:6" x14ac:dyDescent="0.3">
@@ -16042,7 +16072,7 @@
         <v>0.48954822531870601</v>
       </c>
       <c r="F622" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
     </row>
     <row r="623" spans="1:6" x14ac:dyDescent="0.3">
@@ -16062,7 +16092,7 @@
         <v>0.46965826574722402</v>
       </c>
       <c r="F623" t="s">
-        <v>1093</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="624" spans="1:6" x14ac:dyDescent="0.3">
@@ -16082,7 +16112,7 @@
         <v>0.45861922628654</v>
       </c>
       <c r="F624" t="s">
-        <v>1094</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="625" spans="1:6" x14ac:dyDescent="0.3">
@@ -16102,7 +16132,7 @@
         <v>0.45391749149411098</v>
       </c>
       <c r="F625" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
     </row>
     <row r="626" spans="1:6" x14ac:dyDescent="0.3">
@@ -16122,7 +16152,7 @@
         <v>0.45247115048409497</v>
       </c>
       <c r="F626" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
     </row>
     <row r="627" spans="1:6" x14ac:dyDescent="0.3">
@@ -16142,7 +16172,7 @@
         <v>0.41679025746521797</v>
       </c>
       <c r="F627" t="s">
-        <v>1095</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="628" spans="1:6" x14ac:dyDescent="0.3">
@@ -16162,7 +16192,7 @@
         <v>0.40957189006081801</v>
       </c>
       <c r="F628" t="s">
-        <v>1096</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="629" spans="1:6" x14ac:dyDescent="0.3">
@@ -16182,7 +16212,7 @@
         <v>0.405465108108164</v>
       </c>
       <c r="F629" t="s">
-        <v>1097</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="630" spans="1:6" x14ac:dyDescent="0.3">
@@ -16202,7 +16232,7 @@
         <v>0.391489154252191</v>
       </c>
       <c r="F630" t="s">
-        <v>1098</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="631" spans="1:6" x14ac:dyDescent="0.3">
@@ -16222,7 +16252,7 @@
         <v>0.39049758259082801</v>
       </c>
       <c r="F631" t="s">
-        <v>1099</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="632" spans="1:6" x14ac:dyDescent="0.3">
@@ -16242,7 +16272,7 @@
         <v>0.379756751397957</v>
       </c>
       <c r="F632" t="s">
-        <v>1100</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="633" spans="1:6" x14ac:dyDescent="0.3">
@@ -16262,7 +16292,7 @@
         <v>0.36772478012531701</v>
       </c>
       <c r="F633" t="s">
-        <v>1101</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="634" spans="1:6" x14ac:dyDescent="0.3">
@@ -16282,7 +16312,7 @@
         <v>0.314493329902438</v>
       </c>
       <c r="F634" t="s">
-        <v>648</v>
+        <v>644</v>
       </c>
     </row>
     <row r="635" spans="1:6" x14ac:dyDescent="0.3">
@@ -16302,7 +16332,7 @@
         <v>0.31233879432005401</v>
       </c>
       <c r="F635" t="s">
-        <v>1102</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="636" spans="1:6" x14ac:dyDescent="0.3">
@@ -16322,7 +16352,7 @@
         <v>0.23543138210790299</v>
       </c>
       <c r="F636" t="s">
-        <v>1103</v>
+        <v>1099</v>
       </c>
     </row>
   </sheetData>
